--- a/school_data.xlsx
+++ b/school_data.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2996" uniqueCount="2995">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2992" uniqueCount="2991">
   <si>
     <t>学校名称</t>
   </si>
@@ -1127,7 +1127,7 @@
     <t>湖南工程学院</t>
   </si>
   <si>
-    <t>吉林化工学院</t>
+    <t>吉林化工大学</t>
   </si>
   <si>
     <t>中南林业科技大学</t>
@@ -1373,7 +1373,7 @@
     <t>中原工学院</t>
   </si>
   <si>
-    <t>新乡医学院</t>
+    <t>河南医药大学</t>
   </si>
   <si>
     <t>兰州理工大学</t>
@@ -1649,9 +1649,6 @@
     <t>中国人民公安大学</t>
   </si>
   <si>
-    <t>中国青年政治学院</t>
-  </si>
-  <si>
     <t>北京农学院</t>
   </si>
   <si>
@@ -2384,7 +2381,7 @@
     <t>北京体育大学</t>
   </si>
   <si>
-    <t>南昌工程学院</t>
+    <t>江西水利电力大学</t>
   </si>
   <si>
     <t>南昌理工学院</t>
@@ -2666,7 +2663,7 @@
     <t>广东新安职业技术学院</t>
   </si>
   <si>
-    <t>顺德职业技术学院</t>
+    <t>顺德职业技术大学</t>
   </si>
   <si>
     <t>潮汕职业技术学院</t>
@@ -2696,7 +2693,7 @@
     <t>清远职业技术学院</t>
   </si>
   <si>
-    <t>深圳信息职业技术学院</t>
+    <t>深圳信息职业技术大学</t>
   </si>
   <si>
     <t>珠海城市职业技术学院</t>
@@ -3272,10 +3269,10 @@
     <t>澳门理工大学</t>
   </si>
   <si>
-    <t>中国人民解放军战略支援部队信息工程大学</t>
-  </si>
-  <si>
-    <t>陆军勤务学院</t>
+    <t>网络空间部队信息工程大学</t>
+  </si>
+  <si>
+    <t>联勤保障部队工程大学</t>
   </si>
   <si>
     <t>陆军军医大学</t>
@@ -3428,7 +3425,7 @@
     <t>陆军防化学院</t>
   </si>
   <si>
-    <t>中国人民解放军战略支援部队航天工程大学</t>
+    <t>军事航天部队航天工程大学</t>
   </si>
   <si>
     <t>陆军工程大学</t>
@@ -3809,9 +3806,6 @@
     <t>琼台师范学院</t>
   </si>
   <si>
-    <t>上海欧华职业技术学院</t>
-  </si>
-  <si>
     <t>重庆能源职业学院</t>
   </si>
   <si>
@@ -4244,9 +4238,6 @@
     <t>大连软件职业学院</t>
   </si>
   <si>
-    <t>大连翻译职业学院</t>
-  </si>
-  <si>
     <t>大连枫叶职业技术学院</t>
   </si>
   <si>
@@ -4292,7 +4283,7 @@
     <t>甘肃林业职业技术大学</t>
   </si>
   <si>
-    <t>甘肃工业职业技术学院</t>
+    <t>甘肃工业职业技术大学</t>
   </si>
   <si>
     <t>武威职业学院</t>
@@ -5741,7 +5732,7 @@
     <t>陕西工业职业技术学院</t>
   </si>
   <si>
-    <t>杨凌职业技术学院</t>
+    <t>陕西农林职业技术大学</t>
   </si>
   <si>
     <t>陕西能源职业技术学院</t>
@@ -5876,10 +5867,10 @@
     <t>宁夏工业职业学院</t>
   </si>
   <si>
-    <t>宁夏职业技术学院</t>
-  </si>
-  <si>
-    <t>宁夏工商职业技术学院</t>
+    <t>宁夏职业技术大学</t>
+  </si>
+  <si>
+    <t>宁夏工商职业技术大学</t>
   </si>
   <si>
     <t>宁夏财经职业技术学院</t>
@@ -6416,7 +6407,7 @@
     <t>仲恺农业工程学院</t>
   </si>
   <si>
-    <t>广州番禺职业技术学院</t>
+    <t>广州职业技术大学</t>
   </si>
   <si>
     <t>电子科技大学中山学院</t>
@@ -7160,7 +7151,7 @@
     <t>北京卫生职业学院</t>
   </si>
   <si>
-    <t>海军潜艇学院</t>
+    <t>中国人民解放军海军潜艇学院</t>
   </si>
   <si>
     <t>北京理工大学国际教育学院</t>
@@ -7775,7 +7766,7 @@
     <t>大连理工大学盘锦校区</t>
   </si>
   <si>
-    <t>无锡职业技术学院</t>
+    <t>无锡职业技术大学</t>
   </si>
   <si>
     <t>苏州工业园区服务外包职业学院</t>
@@ -7907,9 +7898,6 @@
     <t>辽宁税务高等专科学校</t>
   </si>
   <si>
-    <t>辽宁政法职业学院</t>
-  </si>
-  <si>
     <t>上饶幼儿师范高等专科学校</t>
   </si>
   <si>
@@ -8453,7 +8441,7 @@
     <t>解放军电子工程学院</t>
   </si>
   <si>
-    <t>陆军炮兵防空兵学院</t>
+    <t>陆军兵种大学</t>
   </si>
   <si>
     <t>解放军南京陆军指挥学院</t>
@@ -8699,9 +8687,6 @@
     <t>海军勤务学院</t>
   </si>
   <si>
-    <t>德州理工职业学院</t>
-  </si>
-  <si>
     <t>山东文化艺术职业学院</t>
   </si>
   <si>
@@ -8888,6 +8873,15 @@
     <t>重庆安防职业学院</t>
   </si>
   <si>
+    <t>临沂城市职业学院</t>
+  </si>
+  <si>
+    <t>宁夏交通职业技术学院</t>
+  </si>
+  <si>
+    <t>成都东软学院（中外合作办学项目）</t>
+  </si>
+  <si>
     <t>武警指挥学院</t>
   </si>
   <si>
@@ -8897,9 +8891,6 @@
     <t>中国人民解放军海军士官学校</t>
   </si>
   <si>
-    <t>宁夏交通职业技术学院</t>
-  </si>
-  <si>
     <t>双河职业技术学院</t>
   </si>
   <si>
@@ -8976,9 +8967,6 @@
   </si>
   <si>
     <t>枣庄应用技术职业学院</t>
-  </si>
-  <si>
-    <t>临沂城市职业学院</t>
   </si>
   <si>
     <t>菏泽生物医药职业学院</t>
@@ -9694,6 +9682,13 @@
 </styleSheet>
 </file>
 
+<file path=xl/customStorage/customStorage.xml><?xml version="1.0" encoding="utf-8"?>
+<customStorage xmlns="https://web.wps.cn/et/2018/main">
+  <book/>
+  <sheets/>
+</customStorage>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -9981,7 +9976,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:A2996"/>
+  <dimension ref="A1:A2992"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -22774,22 +22769,22 @@
     </row>
     <row r="2558" spans="1:1">
       <c r="A2558" t="s">
-        <v>2557</v>
+        <v>661</v>
       </c>
     </row>
     <row r="2559" spans="1:1">
       <c r="A2559" t="s">
-        <v>2558</v>
+        <v>2557</v>
       </c>
     </row>
     <row r="2560" spans="1:1">
       <c r="A2560" t="s">
-        <v>2559</v>
+        <v>2558</v>
       </c>
     </row>
     <row r="2561" spans="1:1">
       <c r="A2561" t="s">
-        <v>662</v>
+        <v>2559</v>
       </c>
     </row>
     <row r="2562" spans="1:1">
@@ -24945,26 +24940,6 @@
     <row r="2992" spans="1:1">
       <c r="A2992" t="s">
         <v>2990</v>
-      </c>
-    </row>
-    <row r="2993" spans="1:1">
-      <c r="A2993" t="s">
-        <v>2991</v>
-      </c>
-    </row>
-    <row r="2994" spans="1:1">
-      <c r="A2994" t="s">
-        <v>2992</v>
-      </c>
-    </row>
-    <row r="2995" spans="1:1">
-      <c r="A2995" t="s">
-        <v>2993</v>
-      </c>
-    </row>
-    <row r="2996" spans="1:1">
-      <c r="A2996" t="s">
-        <v>2994</v>
       </c>
     </row>
   </sheetData>

--- a/school_data.xlsx
+++ b/school_data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9324"/>
+    <workbookView windowWidth="28800" windowHeight="12575"/>
   </bookViews>
   <sheets>
     <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2992" uniqueCount="2991">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2983" uniqueCount="2982">
   <si>
     <t>学校名称</t>
   </si>
@@ -2129,7 +2129,7 @@
     <t>成都东软学院</t>
   </si>
   <si>
-    <t>成都航空职业技术学院</t>
+    <t>成都航空职业技术大学</t>
   </si>
   <si>
     <t>成都农业科技职业学院</t>
@@ -2318,7 +2318,7 @@
     <t>天津轻工职业技术学院</t>
   </si>
   <si>
-    <t>天津公安警官职业学院</t>
+    <t>天津警察学院</t>
   </si>
   <si>
     <t>天津机电职业技术学院</t>
@@ -2339,9 +2339,6 @@
     <t>天津工艺美术职业学院</t>
   </si>
   <si>
-    <t>天津开发区职业技术学院</t>
-  </si>
-  <si>
     <t>天津城市职业学院</t>
   </si>
   <si>
@@ -2366,9 +2363,6 @@
     <t>天津铁道职业技术学院</t>
   </si>
   <si>
-    <t>大连商务职业学院</t>
-  </si>
-  <si>
     <t>通辽职业学院</t>
   </si>
   <si>
@@ -2390,7 +2384,7 @@
     <t>江西科技学院</t>
   </si>
   <si>
-    <t>江西中医药高等专科学校</t>
+    <t>抚州医药学院</t>
   </si>
   <si>
     <t>豫章师范学院</t>
@@ -2975,7 +2969,7 @@
     <t>陇东学院</t>
   </si>
   <si>
-    <t>天水师范学院</t>
+    <t>天水师范大学</t>
   </si>
   <si>
     <t>广州南方学院</t>
@@ -3077,9 +3071,6 @@
     <t>东南大学成贤学院</t>
   </si>
   <si>
-    <t>陕西经济管理职业技术学院</t>
-  </si>
-  <si>
     <t>郑州师范学院</t>
   </si>
   <si>
@@ -3170,7 +3161,7 @@
     <t>宿州学院</t>
   </si>
   <si>
-    <t>苏州市职业大学</t>
+    <t>苏州职业技术大学</t>
   </si>
   <si>
     <t>苏州工学院</t>
@@ -3278,9 +3269,6 @@
     <t>陆军军医大学</t>
   </si>
   <si>
-    <t>陆军装甲兵学院</t>
-  </si>
-  <si>
     <t>中国人民解放军空军工程大学</t>
   </si>
   <si>
@@ -3437,7 +3425,7 @@
     <t>武汉纺织大学外经贸学院</t>
   </si>
   <si>
-    <t>中国人民解放军海军航空大学</t>
+    <t>海军航空大学</t>
   </si>
   <si>
     <t>河南工程学院</t>
@@ -3578,9 +3566,6 @@
     <t>河北传媒学院</t>
   </si>
   <si>
-    <t>新疆机电职业技术学院</t>
-  </si>
-  <si>
     <t>海南软件职业技术学院</t>
   </si>
   <si>
@@ -3665,7 +3650,7 @@
     <t>晋城职业技术学院</t>
   </si>
   <si>
-    <t>安徽医学高等专科学校</t>
+    <t>安徽第二医学院</t>
   </si>
   <si>
     <t>南开大学滨海学院</t>
@@ -3701,7 +3686,7 @@
     <t>沧州交通学院</t>
   </si>
   <si>
-    <t>重庆工业职业技术学院</t>
+    <t>重庆工业职业技术大学</t>
   </si>
   <si>
     <t>重庆电力高等专科学校</t>
@@ -3884,7 +3869,7 @@
     <t>安徽涉外经济职业学院</t>
   </si>
   <si>
-    <t>铜仁职业技术学院</t>
+    <t>铜仁职业技术大学</t>
   </si>
   <si>
     <t>安顺职业技术学院</t>
@@ -3905,7 +3890,7 @@
     <t>内蒙古鸿德文理学院</t>
   </si>
   <si>
-    <t>内蒙古建筑职业技术学院</t>
+    <t>内蒙古建筑职业技术大学</t>
   </si>
   <si>
     <t>河北医科大学临床学院</t>
@@ -4031,10 +4016,10 @@
     <t>河套学院</t>
   </si>
   <si>
-    <t>兴安职业技术学院</t>
-  </si>
-  <si>
-    <t>呼和浩特职业学院</t>
+    <t>兴安职业技术大学</t>
+  </si>
+  <si>
+    <t>呼和浩特职业技术大学</t>
   </si>
   <si>
     <t>包头轻工职业技术学院</t>
@@ -4058,12 +4043,6 @@
     <t>内蒙古科技职业学院</t>
   </si>
   <si>
-    <t>内蒙古经贸外语职业学院</t>
-  </si>
-  <si>
-    <t>赤峰职业技术学院</t>
-  </si>
-  <si>
     <t>内蒙古北方职业技术学院</t>
   </si>
   <si>
@@ -4088,7 +4067,7 @@
     <t>长治职业技术学院</t>
   </si>
   <si>
-    <t>山西艺术职业学院</t>
+    <t>山西文化旅游职业大学</t>
   </si>
   <si>
     <t>山西工程职业学院</t>
@@ -4124,12 +4103,6 @@
     <t>潞安职业技术学院</t>
   </si>
   <si>
-    <t>太原旅游职业学院</t>
-  </si>
-  <si>
-    <t>山西旅游职业学院</t>
-  </si>
-  <si>
     <t>山西管理职业学院</t>
   </si>
   <si>
@@ -4199,9 +4172,6 @@
     <t>沈阳航空职业技术学院</t>
   </si>
   <si>
-    <t>辽宁体育运动职业技术学院</t>
-  </si>
-  <si>
     <t>辽宁职业学院</t>
   </si>
   <si>
@@ -4286,7 +4256,7 @@
     <t>甘肃工业职业技术大学</t>
   </si>
   <si>
-    <t>武威职业学院</t>
+    <t>武威职业技术大学</t>
   </si>
   <si>
     <t>甘肃交通职业技术学院</t>
@@ -4415,7 +4385,7 @@
     <t>杭州医学院</t>
   </si>
   <si>
-    <t>宁波职业技术学院</t>
+    <t>宁波职业技术大学</t>
   </si>
   <si>
     <t>温州职业技术学院</t>
@@ -4451,7 +4421,7 @@
     <t>浙江工业职业技术学院</t>
   </si>
   <si>
-    <t>杭州职业技术学院</t>
+    <t>杭州职业技术大学</t>
   </si>
   <si>
     <t>嘉兴职业技术学院</t>
@@ -4526,13 +4496,13 @@
     <t>安庆医药高等专科学校</t>
   </si>
   <si>
-    <t>安徽职业技术学院</t>
+    <t>安徽职业技术大学</t>
   </si>
   <si>
     <t>淮北职业技术学院</t>
   </si>
   <si>
-    <t>芜湖职业技术学院</t>
+    <t>芜湖职业技术大学</t>
   </si>
   <si>
     <t>淮南联合大学</t>
@@ -5504,9 +5474,6 @@
     <t>山东工程职业技术大学</t>
   </si>
   <si>
-    <t>山东杏林科技职业学院</t>
-  </si>
-  <si>
     <t>山东外事职业大学</t>
   </si>
   <si>
@@ -5516,9 +5483,6 @@
     <t>山东现代学院</t>
   </si>
   <si>
-    <t>青岛飞洋职业技术学院</t>
-  </si>
-  <si>
     <t>山东华宇工学院</t>
   </si>
   <si>
@@ -5534,7 +5498,7 @@
     <t>昆明冶金高等专科学校</t>
   </si>
   <si>
-    <t>曲靖医学高等专科学校</t>
+    <t>曲靖健康医学院</t>
   </si>
   <si>
     <t>保山中医药高等专科学校</t>
@@ -5729,7 +5693,7 @@
     <t>西安电力高等专科学校</t>
   </si>
   <si>
-    <t>陕西工业职业技术学院</t>
+    <t>陕西工业职业技术大学</t>
   </si>
   <si>
     <t>陕西农林职业技术大学</t>
@@ -5837,7 +5801,7 @@
     <t>黔西南民族职业技术学院</t>
   </si>
   <si>
-    <t>贵州轻工职业技术学院</t>
+    <t>贵州轻工职业大学</t>
   </si>
   <si>
     <t>贵阳康养职业大学</t>
@@ -6149,7 +6113,7 @@
     <t>湖州学院</t>
   </si>
   <si>
-    <t>绍兴文理学院元培学院</t>
+    <t>绍兴理工学院</t>
   </si>
   <si>
     <t>温州理工学院</t>
@@ -6224,9 +6188,6 @@
     <t>安徽矿业职业技术学院</t>
   </si>
   <si>
-    <t>民办安徽旅游职业学院</t>
-  </si>
-  <si>
     <t>合肥信息技术职业学院</t>
   </si>
   <si>
@@ -6569,7 +6530,7 @@
     <t>黑龙江财经学院</t>
   </si>
   <si>
-    <t>扬州市职业大学</t>
+    <t>扬州职业技术大学</t>
   </si>
   <si>
     <t>南京旅游职业学院</t>
@@ -6716,9 +6677,6 @@
     <t>新疆政法学院</t>
   </si>
   <si>
-    <t>长安大学兴华学院</t>
-  </si>
-  <si>
     <t>青岛远洋船员职业学院</t>
   </si>
   <si>
@@ -6857,9 +6815,6 @@
     <t>陕西工商职业学院</t>
   </si>
   <si>
-    <t>甘肃机电职业技术学院</t>
-  </si>
-  <si>
     <t>天津外国语大学滨海外事学院</t>
   </si>
   <si>
@@ -6869,9 +6824,6 @@
     <t>香港大学</t>
   </si>
   <si>
-    <t>首都师范大学继续教育学院</t>
-  </si>
-  <si>
     <t>福建幼儿师范高等专科学校</t>
   </si>
   <si>
@@ -6968,9 +6920,6 @@
     <t>河北资源环境职业技术学院</t>
   </si>
   <si>
-    <t>山西青年职业学院</t>
-  </si>
-  <si>
     <t>山西传媒学院</t>
   </si>
   <si>
@@ -7133,9 +7082,6 @@
     <t>延边职业技术学院</t>
   </si>
   <si>
-    <t>吉林省教育学院</t>
-  </si>
-  <si>
     <t>济南幼儿师范高等专科学校</t>
   </si>
   <si>
@@ -7328,1678 +7274,1705 @@
     <t>广西职业师范学院</t>
   </si>
   <si>
+    <t>九江科技职业大学</t>
+  </si>
+  <si>
+    <t>渤海理工职业学院</t>
+  </si>
+  <si>
+    <t>白银矿冶职业技术学院</t>
+  </si>
+  <si>
+    <t>香港都会大学</t>
+  </si>
+  <si>
+    <t>香港珠海学院</t>
+  </si>
+  <si>
+    <t>江苏第二师范学院</t>
+  </si>
+  <si>
+    <t>中国科学院大学</t>
+  </si>
+  <si>
+    <t>厦门大学国际学院</t>
+  </si>
+  <si>
+    <t>中国人民大学（苏州校区）</t>
+  </si>
+  <si>
+    <t>甘肃卫生职业学院</t>
+  </si>
+  <si>
+    <t>兰州科技职业学院</t>
+  </si>
+  <si>
+    <t>张家口学院</t>
+  </si>
+  <si>
+    <t>辽宁特殊教育师范高等专科学校</t>
+  </si>
+  <si>
+    <t>四川西南航空职业学院</t>
+  </si>
+  <si>
+    <t>贵州建设职业技术学院</t>
+  </si>
+  <si>
+    <t>山东艺术设计职业学院</t>
+  </si>
+  <si>
+    <t>川南幼儿师范高等专科学校</t>
+  </si>
+  <si>
+    <t>皖北卫生职业学院</t>
+  </si>
+  <si>
+    <t>上海健康医学院</t>
+  </si>
+  <si>
+    <t>四川护理职业学院</t>
+  </si>
+  <si>
+    <t>吉安职业技术学院</t>
+  </si>
+  <si>
+    <t>温州肯恩大学</t>
+  </si>
+  <si>
+    <t>重庆资源与环境保护职业学院</t>
+  </si>
+  <si>
+    <t>成都工贸职业技术学院</t>
+  </si>
+  <si>
+    <t>香港中文大学（深圳）</t>
+  </si>
+  <si>
+    <t>成都工业职业技术学院</t>
+  </si>
+  <si>
+    <t>贵州工程职业学院</t>
+  </si>
+  <si>
+    <t>黑龙江冰雪体育职业学院</t>
+  </si>
+  <si>
+    <t>广西培贤国际职业学院</t>
+  </si>
+  <si>
+    <t>惠州城市职业学院</t>
+  </si>
+  <si>
+    <t>广州卫生职业技术学院</t>
+  </si>
+  <si>
+    <t>内蒙古民族幼儿师范高等专科学校</t>
+  </si>
+  <si>
+    <t>广东酒店管理职业技术学院</t>
+  </si>
+  <si>
+    <t>南阳农业职业学院</t>
+  </si>
+  <si>
+    <t>内蒙古艺术学院</t>
+  </si>
+  <si>
+    <t>北京网络职业学院</t>
+  </si>
+  <si>
+    <t>烟台黄金职业学院</t>
+  </si>
+  <si>
+    <t>广西金融职业技术学院</t>
+  </si>
+  <si>
+    <t>贵阳幼儿师范高等专科学校</t>
+  </si>
+  <si>
+    <t>扎兰屯职业学院</t>
+  </si>
+  <si>
+    <t>鄂尔多斯生态环境职业学院</t>
+  </si>
+  <si>
+    <t>威海海洋职业学院</t>
+  </si>
+  <si>
+    <t>湛江幼儿师范专科学校</t>
+  </si>
+  <si>
+    <t>辽宁民族师范高等专科学校</t>
+  </si>
+  <si>
+    <t>铜仁幼儿师范高等专科学校</t>
+  </si>
+  <si>
+    <t>南通师范高等专科学校</t>
+  </si>
+  <si>
+    <t>贵州工贸职业学院</t>
+  </si>
+  <si>
+    <t>贵州应用技术职业学院</t>
+  </si>
+  <si>
+    <t>贵州水利水电职业技术学院</t>
+  </si>
+  <si>
+    <t>贵州农业职业学院</t>
+  </si>
+  <si>
+    <t>毕节医学高等专科学校</t>
+  </si>
+  <si>
+    <t>广东茂名健康职业学院</t>
+  </si>
+  <si>
+    <t>广东碧桂园职业学院</t>
+  </si>
+  <si>
+    <t>广东茂名幼儿师范专科学校</t>
+  </si>
+  <si>
+    <t>广东生态工程职业学院</t>
+  </si>
+  <si>
+    <t>广东以色列理工学院</t>
+  </si>
+  <si>
+    <t>香港树仁大学</t>
+  </si>
+  <si>
+    <t>澳门城市大学</t>
+  </si>
+  <si>
+    <t>安徽公安职业学院</t>
+  </si>
+  <si>
+    <t>南昌影视传播职业学院</t>
+  </si>
+  <si>
+    <t>江西水利职业学院</t>
+  </si>
+  <si>
+    <t>深圳北理莫斯科大学</t>
+  </si>
+  <si>
+    <t>江西洪州职业学院</t>
+  </si>
+  <si>
+    <t>江西师范高等专科学校</t>
+  </si>
+  <si>
+    <t>中国社会科学院大学</t>
+  </si>
+  <si>
+    <t>哈尔滨工业大学（深圳）</t>
+  </si>
+  <si>
+    <t>阜阳幼儿师范高等专科学校</t>
+  </si>
+  <si>
+    <t>陕西机电职业技术学院</t>
+  </si>
+  <si>
+    <t>福州墨尔本理工职业学院</t>
+  </si>
+  <si>
+    <t>长春健康职业学院</t>
+  </si>
+  <si>
+    <t>浙江音乐学院</t>
+  </si>
+  <si>
+    <t>广西安全工程职业技术学院</t>
+  </si>
+  <si>
+    <t>海南体育职业技术学院</t>
+  </si>
+  <si>
+    <t>哈尔滨音乐学院</t>
+  </si>
+  <si>
+    <t>鄂尔多斯应用技术学院</t>
+  </si>
+  <si>
+    <t>滇西应用技术大学</t>
+  </si>
+  <si>
+    <t>曹妃甸职业技术学院</t>
+  </si>
+  <si>
+    <t>云南财经职业学院</t>
+  </si>
+  <si>
+    <t>贵州健康职业学院</t>
+  </si>
+  <si>
+    <t>毕节幼儿师范高等专科学校</t>
+  </si>
+  <si>
+    <t>重庆护理职业学院</t>
+  </si>
+  <si>
+    <t>三亚中瑞酒店管理职业学院</t>
+  </si>
+  <si>
+    <t>云南医药健康职业学院</t>
+  </si>
+  <si>
+    <t>茅台学院</t>
+  </si>
+  <si>
+    <t>新疆工业职业技术学院</t>
+  </si>
+  <si>
+    <t>运城师范高等专科学校</t>
+  </si>
+  <si>
+    <t>朔州师范高等专科学校</t>
+  </si>
+  <si>
+    <t>武汉铁路桥梁职业学院</t>
+  </si>
+  <si>
+    <t>青海柴达木职业技术学院</t>
+  </si>
+  <si>
+    <t>哈密职业技术学院</t>
+  </si>
+  <si>
+    <t>海南健康管理职业技术学院</t>
+  </si>
+  <si>
+    <t>深圳技术大学</t>
+  </si>
+  <si>
+    <t>中国石油大学（北京）克拉玛依校区</t>
+  </si>
+  <si>
+    <t>闽江师范高等专科学校</t>
+  </si>
+  <si>
+    <t>兰州现代职业学院</t>
+  </si>
+  <si>
+    <t>甘肃财贸职业学院</t>
+  </si>
+  <si>
+    <t>贵州电子科技职业学院</t>
+  </si>
+  <si>
+    <t>临夏现代职业学院</t>
+  </si>
+  <si>
+    <t>平凉职业技术学院</t>
+  </si>
+  <si>
+    <t>太原幼儿师范高等专科学校</t>
+  </si>
+  <si>
+    <t>湘中幼儿师范高等专科学校</t>
+  </si>
+  <si>
+    <t>贵州电子商务职业技术学院</t>
+  </si>
+  <si>
+    <t>贵州护理职业技术学院</t>
+  </si>
+  <si>
+    <t>贵州食品工程职业学院</t>
+  </si>
+  <si>
+    <t>贵州装备制造职业学院</t>
+  </si>
+  <si>
+    <t>黔南民族幼儿师范高等专科学校</t>
+  </si>
+  <si>
+    <t>贵州经贸职业技术学院</t>
+  </si>
+  <si>
+    <t>青海高等职业技术学院</t>
+  </si>
+  <si>
+    <t>吐鲁番职业技术学院</t>
+  </si>
+  <si>
+    <t>博尔塔拉职业技术学院</t>
+  </si>
+  <si>
+    <t>新疆生产建设兵团兴新职业技术学院</t>
+  </si>
+  <si>
+    <t>昭通卫生职业学院</t>
+  </si>
+  <si>
+    <t>云南交通运输职业学院</t>
+  </si>
+  <si>
+    <t>昆明铁道职业技术学院</t>
+  </si>
+  <si>
+    <t>大理护理职业学院</t>
+  </si>
+  <si>
+    <t>云南水利水电职业学院</t>
+  </si>
+  <si>
+    <t>宜春幼儿师范高等专科学校</t>
+  </si>
+  <si>
+    <t>广东江门中医药职业学院</t>
+  </si>
+  <si>
+    <t>惠州工程职业学院</t>
+  </si>
+  <si>
+    <t>长春师范高等专科学校</t>
+  </si>
+  <si>
+    <t>吉林水利电力职业学院</t>
+  </si>
+  <si>
+    <t>天津体育职业学院</t>
+  </si>
+  <si>
+    <t>天津滨海汽车工程职业学院</t>
+  </si>
+  <si>
+    <t>石家庄城市经济职业学院</t>
+  </si>
+  <si>
+    <t>唐山幼儿师范高等专科学校</t>
+  </si>
+  <si>
+    <t>吉林职业技术学院</t>
+  </si>
+  <si>
+    <t>泉州工程职业技术学院</t>
+  </si>
+  <si>
+    <t>四川应用技术职业学院</t>
+  </si>
+  <si>
+    <t>西藏农牧大学</t>
+  </si>
+  <si>
+    <t>贵州航空职业技术学院</t>
+  </si>
+  <si>
+    <t>华北理工大学冀唐学院</t>
+  </si>
+  <si>
+    <t>浙江特殊教育职业学院</t>
+  </si>
+  <si>
+    <t>浙江安防职业技术学院</t>
+  </si>
+  <si>
+    <t>浙江舟山群岛新区旅游与健康职业学院</t>
+  </si>
+  <si>
+    <t>红河卫生职业学院</t>
+  </si>
+  <si>
+    <t>大理农林职业技术学院</t>
+  </si>
+  <si>
+    <t>云南特殊教育职业学院</t>
+  </si>
+  <si>
+    <t>吕梁职业技术学院</t>
+  </si>
+  <si>
+    <t>菏泽职业学院</t>
+  </si>
+  <si>
+    <t>山东特殊教育职业学院</t>
+  </si>
+  <si>
+    <t>日照航海工程职业学院</t>
+  </si>
+  <si>
+    <t>西宁城市职业技术学院</t>
+  </si>
+  <si>
+    <t>江西卫生职业学院</t>
+  </si>
+  <si>
+    <t>江西医学高等专科学校</t>
+  </si>
+  <si>
+    <t>赣南卫生健康职业学院</t>
+  </si>
+  <si>
+    <t>大连理工大学盘锦校区</t>
+  </si>
+  <si>
+    <t>无锡职业技术大学</t>
+  </si>
+  <si>
+    <t>苏州工业园区服务外包职业学院</t>
+  </si>
+  <si>
+    <t>江苏财会职业学院</t>
+  </si>
+  <si>
+    <t>南京审计大学金审学院</t>
+  </si>
+  <si>
+    <t>昆山杜克大学</t>
+  </si>
+  <si>
+    <t>盐城幼儿师范高等专科学校</t>
+  </si>
+  <si>
+    <t>苏州幼儿师范高等专科学校</t>
+  </si>
+  <si>
+    <t>江苏城乡建设职业学院</t>
+  </si>
+  <si>
+    <t>江苏安全技术职业学院</t>
+  </si>
+  <si>
+    <t>江苏旅游职业学院</t>
+  </si>
+  <si>
+    <t>湖南幼儿师范高等专科学校</t>
+  </si>
+  <si>
+    <t>湖南财经工业职业技术学院</t>
+  </si>
+  <si>
+    <t>湘南幼儿师范高等专科学校</t>
+  </si>
+  <si>
+    <t>武汉光谷职业学院</t>
+  </si>
+  <si>
+    <t>湖北幼儿师范高等专科学校</t>
+  </si>
+  <si>
+    <t>湖北铁道运输职业学院</t>
+  </si>
+  <si>
+    <t>武汉海事职业学院</t>
+  </si>
+  <si>
+    <t>长江艺术工程职业学院</t>
+  </si>
+  <si>
+    <t>荆门职业学院</t>
+  </si>
+  <si>
+    <t>黑龙江公安警官职业学院</t>
+  </si>
+  <si>
+    <t>河南应用技术职业学院</t>
+  </si>
+  <si>
+    <t>郑州信息工程职业学院</t>
+  </si>
+  <si>
+    <t>河南林业职业学院</t>
+  </si>
+  <si>
+    <t>濮阳医学高等专科学校</t>
+  </si>
+  <si>
+    <t>河南轻工职业学院</t>
+  </si>
+  <si>
+    <t>驻马店幼儿师范高等专科学校</t>
+  </si>
+  <si>
+    <t>郑州财税金融职业学院</t>
+  </si>
+  <si>
+    <t>三门峡社会管理职业学院</t>
+  </si>
+  <si>
+    <t>河南测绘职业学院</t>
+  </si>
+  <si>
+    <t>鹤壁能源化工职业学院</t>
+  </si>
+  <si>
+    <t>平顶山文化艺术职业学院</t>
+  </si>
+  <si>
+    <t>保定幼儿师范高等专科学校</t>
+  </si>
+  <si>
+    <t>河北工艺美术职业学院</t>
+  </si>
+  <si>
+    <t>衡水职业技术学院</t>
+  </si>
+  <si>
+    <t>新疆科技职业技术学院</t>
+  </si>
+  <si>
+    <t>巴中职业技术学院</t>
+  </si>
+  <si>
+    <t>上海公安学院</t>
+  </si>
+  <si>
+    <t>阳泉职业技术学院</t>
+  </si>
+  <si>
+    <t>宁夏幼儿师范高等专科学校</t>
+  </si>
+  <si>
+    <t>宁夏艺术职业学院</t>
+  </si>
+  <si>
+    <t>宁夏体育职业学院</t>
+  </si>
+  <si>
+    <t>沈阳化工大学</t>
+  </si>
+  <si>
+    <t>沈阳理工大学</t>
+  </si>
+  <si>
+    <t>辽宁税务高等专科学校</t>
+  </si>
+  <si>
+    <t>上饶幼儿师范高等专科学校</t>
+  </si>
+  <si>
+    <t>抚州幼儿师范高等专科学校</t>
+  </si>
+  <si>
+    <t>江苏联合职业技术学院</t>
+  </si>
+  <si>
+    <t>扬州中瑞酒店职业学院</t>
+  </si>
+  <si>
+    <t>江苏航空职业技术学院</t>
+  </si>
+  <si>
+    <t>湖南工商职业学院</t>
+  </si>
+  <si>
+    <t>湖南吉利汽车职业技术学院</t>
+  </si>
+  <si>
+    <t>湖南劳动人事职业学院</t>
+  </si>
+  <si>
+    <t>湖北职业技术学院</t>
+  </si>
+  <si>
+    <t>天府新区信息职业学院</t>
+  </si>
+  <si>
+    <t>天府新区通用航空职业学院</t>
+  </si>
+  <si>
+    <t>辽宁生态工程职业学院</t>
+  </si>
+  <si>
+    <t>桂林生命与健康职业技术学院</t>
+  </si>
+  <si>
+    <t>江阳城建职业学院</t>
+  </si>
+  <si>
+    <t>承德应用技术职业学院</t>
+  </si>
+  <si>
+    <t>哈尔滨北方航空职业技术学院</t>
+  </si>
+  <si>
+    <t>广元中核职业技术学院</t>
+  </si>
+  <si>
+    <t>南昌大学抚州医学院</t>
+  </si>
+  <si>
+    <t>郑州西亚斯学院</t>
+  </si>
+  <si>
+    <t>石河子工程职业技术学院</t>
+  </si>
+  <si>
+    <t>资阳口腔职业学院</t>
+  </si>
+  <si>
+    <t>眉山药科职业学院</t>
+  </si>
+  <si>
+    <t>神木职业技术学院</t>
+  </si>
+  <si>
+    <t>西安健康工程职业学院</t>
+  </si>
+  <si>
+    <t>福建技术师范学院</t>
+  </si>
+  <si>
+    <t>西昌民族幼儿师范高等专科学校</t>
+  </si>
+  <si>
+    <t>达州中医药职业学院</t>
+  </si>
+  <si>
+    <t>赣州职业技术学院</t>
+  </si>
+  <si>
+    <t>中国消防救援学院</t>
+  </si>
+  <si>
+    <t>海南卫生健康职业学院</t>
+  </si>
+  <si>
+    <t>西南财经大学特拉华数据科学学院</t>
+  </si>
+  <si>
+    <t>毕节工业职业技术学院</t>
+  </si>
+  <si>
+    <t>大同师范高等专科学校</t>
+  </si>
+  <si>
+    <t>云南工贸职业技术学院</t>
+  </si>
+  <si>
+    <t>云南理工职业学院</t>
+  </si>
+  <si>
+    <t>云南轻纺职业学院</t>
+  </si>
+  <si>
+    <t>信阳航空职业学院</t>
+  </si>
+  <si>
+    <t>六盘水幼儿师范高等专科学校</t>
+  </si>
+  <si>
+    <t>内江卫生与健康职业学院</t>
+  </si>
+  <si>
+    <t>南充科技职业学院</t>
+  </si>
+  <si>
+    <t>四川体育职业学院</t>
+  </si>
+  <si>
+    <t>天府新区航空旅游职业学院</t>
+  </si>
+  <si>
+    <t>安徽艺术学院</t>
+  </si>
+  <si>
+    <t>宝鸡三和职业学院</t>
+  </si>
+  <si>
+    <t>广东江门幼儿师范高等专科学校</t>
+  </si>
+  <si>
+    <t>广东茂名农林科技职业学院</t>
+  </si>
+  <si>
+    <t>广东财贸职业学院</t>
+  </si>
+  <si>
+    <t>广西自然资源职业技术学院</t>
+  </si>
+  <si>
+    <t>广西蓝天航空职业学院</t>
+  </si>
+  <si>
+    <t>德阳城市轨道交通职业学院</t>
+  </si>
+  <si>
+    <t>德阳科贸职业学院</t>
+  </si>
+  <si>
+    <t>怀化师范高等专科学校</t>
+  </si>
+  <si>
+    <t>攀枝花攀西职业学院</t>
+  </si>
+  <si>
+    <t>新疆科信职业技术学院</t>
+  </si>
+  <si>
+    <t>曲靖职业技术学院</t>
+  </si>
+  <si>
+    <t>江西婺源茶业职业学院</t>
+  </si>
+  <si>
+    <t>江西软件职业技术大学</t>
+  </si>
+  <si>
+    <t>河南地矿职业学院</t>
+  </si>
+  <si>
+    <t>河南物流职业学院</t>
+  </si>
+  <si>
+    <t>玉柴职业技术学院</t>
+  </si>
+  <si>
+    <t>萍乡卫生职业学院</t>
+  </si>
+  <si>
+    <t>西湖大学</t>
+  </si>
+  <si>
+    <t>资阳环境科技职业学院</t>
+  </si>
+  <si>
+    <t>郑州亚欧交通职业学院</t>
+  </si>
+  <si>
+    <t>郑州卫生健康职业学院</t>
+  </si>
+  <si>
+    <t>阿坝职业学院</t>
+  </si>
+  <si>
+    <t>重庆健康职业学院</t>
+  </si>
+  <si>
+    <t>昆明幼儿师范高等专科学校</t>
+  </si>
+  <si>
+    <t>江西管理职业学院</t>
+  </si>
+  <si>
+    <t>铁门关职业技术学院</t>
+  </si>
+  <si>
+    <t>克孜勒苏职业技术学院</t>
+  </si>
+  <si>
+    <t>和田职业技术学院</t>
+  </si>
+  <si>
+    <t>青岛工程职业学院</t>
+  </si>
+  <si>
+    <t>株洲师范高等专科学校</t>
+  </si>
+  <si>
+    <t>邯郸幼儿师范高等专科学校</t>
+  </si>
+  <si>
+    <t>贵州机电职业技术学院</t>
+  </si>
+  <si>
+    <t>贵州财经职业学院</t>
+  </si>
+  <si>
+    <t>贵州民用航空职业学院</t>
+  </si>
+  <si>
+    <t>重庆智能工程职业学院</t>
+  </si>
+  <si>
+    <t>重庆理工职业学院</t>
+  </si>
+  <si>
+    <t>九江理工职业学院</t>
+  </si>
+  <si>
+    <t>长春早期教育职业学院</t>
+  </si>
+  <si>
+    <t>黄山健康职业学院</t>
+  </si>
+  <si>
+    <t>南充电影工业职业学院</t>
+  </si>
+  <si>
+    <t>鞍山职业技术学院</t>
+  </si>
+  <si>
+    <t>浙江宇翔职业技术学院</t>
+  </si>
+  <si>
+    <t>南昌健康职业技术学院</t>
+  </si>
+  <si>
+    <t>青岛航空科技职业学院</t>
+  </si>
+  <si>
+    <t>永州师范高等专科学校</t>
+  </si>
+  <si>
+    <t>林州建筑职业技术学院</t>
+  </si>
+  <si>
+    <t>广西制造工程职业技术学院</t>
+  </si>
+  <si>
+    <t>河南女子职业学院</t>
+  </si>
+  <si>
+    <t>南阳科技职业学院</t>
+  </si>
+  <si>
+    <t>潍坊环境工程职业学院</t>
+  </si>
+  <si>
+    <t>河南对外经济贸易职业学院</t>
+  </si>
+  <si>
+    <t>绵阳飞行职业学院</t>
+  </si>
+  <si>
+    <t>梅河口康美职业技术学院</t>
+  </si>
+  <si>
+    <t>长沙幼儿师范高等专科学校</t>
+  </si>
+  <si>
+    <t>邯郸科技职业学院</t>
+  </si>
+  <si>
+    <t>烟台文化旅游职业学院</t>
+  </si>
+  <si>
+    <t>复旦大学上海医学院</t>
+  </si>
+  <si>
+    <t>合肥工业大学宣城校区</t>
+  </si>
+  <si>
+    <t>赤峰应用技术职业学院</t>
+  </si>
+  <si>
+    <t>衡阳幼儿师范高等专科学校</t>
+  </si>
+  <si>
+    <t>榆林能源科技职业学院</t>
+  </si>
+  <si>
+    <t>培黎职业学院</t>
+  </si>
+  <si>
+    <t>石嘴山工贸职业技术学院</t>
+  </si>
+  <si>
+    <t>德阳农业科技职业学院</t>
+  </si>
+  <si>
+    <t>南充文化旅游职业学院</t>
+  </si>
+  <si>
+    <t>广西物流职业技术学院</t>
+  </si>
+  <si>
+    <t>湖北健康职业学院</t>
+  </si>
+  <si>
+    <t>郑州体育职业学院</t>
+  </si>
+  <si>
+    <t>汝州职业技术学院</t>
+  </si>
+  <si>
+    <t>兰考三农职业学院</t>
+  </si>
+  <si>
+    <t>濮阳石油化工职业技术学院</t>
+  </si>
+  <si>
+    <t>临沂科技职业学院</t>
+  </si>
+  <si>
+    <t>朔州陶瓷职业技术学院</t>
+  </si>
+  <si>
+    <t>唐山海运职业学院</t>
+  </si>
+  <si>
+    <t>梧州医学高等专科学校</t>
+  </si>
+  <si>
+    <t>钦州幼儿师范高等专科学校</t>
+  </si>
+  <si>
+    <t>江苏海洋大学</t>
+  </si>
+  <si>
+    <t>辽宁师范高等专科学校</t>
+  </si>
+  <si>
+    <t>浙江警察学院</t>
+  </si>
+  <si>
+    <t>云南中医药大学</t>
+  </si>
+  <si>
+    <t>烟台幼儿师范高等专科学校</t>
+  </si>
+  <si>
+    <t>广州幼儿师范高等专科学校</t>
+  </si>
+  <si>
+    <t>中国人民解放军陆军步兵学院</t>
+  </si>
+  <si>
+    <t>中国人民解放军陆军特种作战学院</t>
+  </si>
+  <si>
+    <t>中国人民解放军陆军边海防学院</t>
+  </si>
+  <si>
+    <t>重庆移通学院德国工程学院</t>
+  </si>
+  <si>
+    <t>香港恒生大学</t>
+  </si>
+  <si>
+    <t>邢台应用技术职业学院</t>
+  </si>
+  <si>
+    <t>吉林通用航空职业技术学院</t>
+  </si>
+  <si>
+    <t>通化医药健康职业学院</t>
+  </si>
+  <si>
+    <t>上海南湖职业技术学院</t>
+  </si>
+  <si>
+    <t>浙江金华科贸职业技术学院</t>
+  </si>
+  <si>
+    <t>宿州航空职业学院</t>
+  </si>
+  <si>
+    <t>和君职业学院</t>
+  </si>
+  <si>
+    <t>湖北孝感美珈职业学院</t>
+  </si>
+  <si>
+    <t>广东梅州职业技术学院</t>
+  </si>
+  <si>
+    <t>广东潮州卫生健康职业学院</t>
+  </si>
+  <si>
+    <t>广东云浮中医药职业学院</t>
+  </si>
+  <si>
+    <t>防城港职业技术学院</t>
+  </si>
+  <si>
+    <t>广西信息职业技术学院</t>
+  </si>
+  <si>
+    <t>广西农业工程职业技术学院</t>
+  </si>
+  <si>
+    <t>北海康养职业学院</t>
+  </si>
+  <si>
+    <t>甘孜职业学院</t>
+  </si>
+  <si>
+    <t>贵州文化旅游职业学院</t>
+  </si>
+  <si>
+    <t>自贡职业技术学院</t>
+  </si>
+  <si>
+    <t>宝鸡中北职业学院</t>
+  </si>
+  <si>
+    <t>兰州航空职业技术学院</t>
+  </si>
+  <si>
+    <t>白银希望职业技术学院</t>
+  </si>
+  <si>
+    <t>滨州科技职业学院</t>
+  </si>
+  <si>
+    <t>重庆工信职业学院</t>
+  </si>
+  <si>
+    <t>郑州医药健康职业学院</t>
+  </si>
+  <si>
+    <t>郑州城建职业学院</t>
+  </si>
+  <si>
+    <t>信阳艺术职业学院</t>
+  </si>
+  <si>
+    <t>周口文理职业学院</t>
+  </si>
+  <si>
+    <t>洛阳文化旅游职业学院</t>
+  </si>
+  <si>
+    <t>长治幼儿师范高等专科学校</t>
+  </si>
+  <si>
+    <t>红河职业技术学院</t>
+  </si>
+  <si>
+    <t>塔城职业技术学院</t>
+  </si>
+  <si>
+    <t>塔里木职业技术学院</t>
+  </si>
+  <si>
+    <t>泸州医疗器械职业学院</t>
+  </si>
+  <si>
+    <t>郑州轨道工程职业学院</t>
+  </si>
+  <si>
+    <t>郑州电子商务职业学院</t>
+  </si>
+  <si>
+    <t>山西通用航空职业技术学院</t>
+  </si>
+  <si>
+    <t>青岛幼儿师范高等专科学校</t>
+  </si>
+  <si>
+    <t>阿勒泰职业技术学院</t>
+  </si>
+  <si>
+    <t>喀什职业技术学院</t>
+  </si>
+  <si>
+    <t>浙江大学医学院</t>
+  </si>
+  <si>
+    <t>解放军国际关系学院</t>
+  </si>
+  <si>
+    <t>中国人民解放军西安通信学院</t>
+  </si>
+  <si>
+    <t>解放军陆军航空兵学院</t>
+  </si>
+  <si>
+    <t>西藏警官高等专科学校</t>
+  </si>
+  <si>
+    <t>空军勤务学院</t>
+  </si>
+  <si>
+    <t>中国人民解放军海军大连舰艇学院</t>
+  </si>
+  <si>
+    <t>海军工程大学</t>
+  </si>
+  <si>
+    <t>空军航空大学</t>
+  </si>
+  <si>
+    <t>解放军电子工程学院</t>
+  </si>
+  <si>
+    <t>陆军兵种大学</t>
+  </si>
+  <si>
+    <t>解放军南京陆军指挥学院</t>
+  </si>
+  <si>
+    <t>解放军工程兵学院</t>
+  </si>
+  <si>
+    <t>空军指挥学院</t>
+  </si>
+  <si>
+    <t>解放军空军第一航空学院</t>
+  </si>
+  <si>
+    <t>解放军空军西安飞行学院</t>
+  </si>
+  <si>
+    <t>解放军装甲兵学院</t>
+  </si>
+  <si>
+    <t>解放军装甲兵技术学院</t>
+  </si>
+  <si>
+    <t>海军指挥学院</t>
+  </si>
+  <si>
+    <t>广东汕头幼儿师范高等专科学校</t>
+  </si>
+  <si>
+    <t>西南大学西塔学院</t>
+  </si>
+  <si>
+    <t>重庆医科大学国际医学院</t>
+  </si>
+  <si>
+    <t>广东肇庆航空职业学院</t>
+  </si>
+  <si>
+    <t>重庆五一职业技术学院</t>
+  </si>
+  <si>
+    <t>益阳师范高等专科学校</t>
+  </si>
+  <si>
+    <t>贵州大学北阿拉巴马国际工程技术学院</t>
+  </si>
+  <si>
+    <t>常州幼儿师范高等专科学校</t>
+  </si>
+  <si>
+    <t>娄底幼儿师范高等专科学校</t>
+  </si>
+  <si>
+    <t>吕梁师范高等专科学校</t>
+  </si>
+  <si>
+    <t>上海科创职业技术学院</t>
+  </si>
+  <si>
+    <t>上海闵行职业技术学院</t>
+  </si>
+  <si>
+    <t>上海现代化工职业学院</t>
+  </si>
+  <si>
+    <t>上海建设管理职业技术学院</t>
+  </si>
+  <si>
+    <t>玉溪职业技术学院</t>
+  </si>
+  <si>
+    <t>保山职业学院</t>
+  </si>
+  <si>
+    <t>昭通职业学院</t>
+  </si>
+  <si>
+    <t>重庆中医药学院</t>
+  </si>
+  <si>
+    <t>郑州汽车工程职业学院</t>
+  </si>
+  <si>
+    <t>周口理工职业学院</t>
+  </si>
+  <si>
+    <t>秦皇岛工业职业技术学院</t>
+  </si>
+  <si>
+    <t>广西质量工程职业技术学院</t>
+  </si>
+  <si>
+    <t>潍坊食品科技职业学院</t>
+  </si>
+  <si>
+    <t>贵州铜仁数据职业学院</t>
+  </si>
+  <si>
+    <t>新星职业技术学院</t>
+  </si>
+  <si>
+    <t>上饶卫生健康职业学院</t>
+  </si>
+  <si>
+    <t>可克达拉职业技术学院</t>
+  </si>
+  <si>
+    <t>海南比勒费尔德应用科学大学</t>
+  </si>
+  <si>
+    <t>图木舒克职业技术学院</t>
+  </si>
+  <si>
+    <t>贵州体育职业学院</t>
+  </si>
+  <si>
+    <t>新疆司法警官职业学院</t>
+  </si>
+  <si>
+    <t>郑州美术学院</t>
+  </si>
+  <si>
+    <t>衡水健康科技职业学院</t>
+  </si>
+  <si>
+    <t>沧州航空职业学院</t>
+  </si>
+  <si>
+    <t>邯郸应用技术职业学院</t>
+  </si>
+  <si>
+    <t>山东城市服务职业学院</t>
+  </si>
+  <si>
+    <t>南阳工艺美术职业学院</t>
+  </si>
+  <si>
+    <t>濮阳科技职业学院</t>
+  </si>
+  <si>
+    <t>开封职业学院</t>
+  </si>
+  <si>
+    <t>郑州软件职业技术学院</t>
+  </si>
+  <si>
+    <t>郑州智能科技职业学院</t>
+  </si>
+  <si>
+    <t>襄阳科技职业学院</t>
+  </si>
+  <si>
+    <t>宜昌科技职业学院</t>
+  </si>
+  <si>
+    <t>邵阳工业职业技术学院</t>
+  </si>
+  <si>
+    <t>长沙轨道交通职业学院</t>
+  </si>
+  <si>
+    <t>岳阳现代服务职业学院</t>
+  </si>
+  <si>
+    <t>衡阳科技职业学院</t>
+  </si>
+  <si>
+    <t>香港科技大学（广州）</t>
+  </si>
+  <si>
+    <t>珠海格力职业学院</t>
+  </si>
+  <si>
+    <t>丽江职业技术学院</t>
+  </si>
+  <si>
+    <t>遂宁能源职业学院</t>
+  </si>
+  <si>
+    <t>遂宁工程职业学院</t>
+  </si>
+  <si>
+    <t>遂宁职业学院</t>
+  </si>
+  <si>
+    <t>文山职业技术学院</t>
+  </si>
+  <si>
+    <t>香格里拉职业学院</t>
+  </si>
+  <si>
+    <t>定西职业技术学院</t>
+  </si>
+  <si>
+    <t>宁夏卫生健康职业技术学院</t>
+  </si>
+  <si>
+    <t>阿克苏工业职业技术学院</t>
+  </si>
+  <si>
+    <t>喀什理工职业技术学院</t>
+  </si>
+  <si>
+    <t>昆玉职业技术学院</t>
+  </si>
+  <si>
+    <t>长沙文创艺术职业学院</t>
+  </si>
+  <si>
+    <t>洛阳商业职业学院</t>
+  </si>
+  <si>
+    <t>常德科技职业技术学院</t>
+  </si>
+  <si>
+    <t>桂林信息工程职业学院</t>
+  </si>
+  <si>
+    <t>郴州思科职业学院</t>
+  </si>
+  <si>
+    <t>重庆数字产业职业技术学院</t>
+  </si>
+  <si>
+    <t>长春数字科技职业学院</t>
+  </si>
+  <si>
+    <t>烟台城市科技职业学院</t>
+  </si>
+  <si>
+    <t>吉安幼儿师范高等专科学校</t>
+  </si>
+  <si>
+    <t>香港城市大学（东莞）</t>
+  </si>
+  <si>
+    <t>安徽公安学院</t>
+  </si>
+  <si>
+    <t>中国人民武装警察部队特种警察学院</t>
+  </si>
+  <si>
+    <t>海军勤务学院</t>
+  </si>
+  <si>
+    <t>山东文化艺术职业学院</t>
+  </si>
+  <si>
+    <t>日照康养职业学院</t>
+  </si>
+  <si>
+    <t>烟台卫生健康职业学院</t>
+  </si>
+  <si>
+    <t>贵州传媒职业学院</t>
+  </si>
+  <si>
+    <t>江苏司法警官职业学院</t>
+  </si>
+  <si>
+    <t>蚌埠城市轨道交通职业学院</t>
+  </si>
+  <si>
+    <t>海南东方新丝路职业学院</t>
+  </si>
+  <si>
+    <t>贵州生态能源职业学院</t>
+  </si>
+  <si>
+    <t>黔东南理工职业学院</t>
+  </si>
+  <si>
+    <t>康复大学</t>
+  </si>
+  <si>
+    <t>深圳理工大学</t>
+  </si>
+  <si>
+    <t>商丘幼儿师范高等专科学校</t>
+  </si>
+  <si>
+    <t>华北水利水电大学乌拉尔学院</t>
+  </si>
+  <si>
+    <t>郑州食品工程职业学院</t>
+  </si>
+  <si>
+    <t>焦作新材料职业学院</t>
+  </si>
+  <si>
+    <t>江西樟树中医药职业学院</t>
+  </si>
+  <si>
+    <t>海南医科大学西英格兰学院</t>
+  </si>
+  <si>
+    <t>青海理工学院</t>
+  </si>
+  <si>
+    <t>赣东职业技术学院</t>
+  </si>
+  <si>
+    <t>河南体育学院</t>
+  </si>
+  <si>
+    <t>芜湖航空职业学院</t>
+  </si>
+  <si>
+    <t>上海浦东职业技术学院</t>
+  </si>
+  <si>
+    <t>芜湖医药健康职业学院</t>
+  </si>
+  <si>
+    <t>怒江职业技术学院</t>
+  </si>
+  <si>
+    <t>长沙医药健康职业学院</t>
+  </si>
+  <si>
+    <t>海南艺术职业学院</t>
+  </si>
+  <si>
+    <t>玉林职业技术学院</t>
+  </si>
+  <si>
+    <t>海口旅游职业学院</t>
+  </si>
+  <si>
+    <t>三亚护理职业学院</t>
+  </si>
+  <si>
+    <t>广西智能制造职业技术学院</t>
+  </si>
+  <si>
+    <t>深圳城市职业学院</t>
+  </si>
+  <si>
+    <t>盐城农业科技职业学院</t>
+  </si>
+  <si>
+    <t>驻马店农业工程职业学院</t>
+  </si>
+  <si>
+    <t>宿迁幼儿师范高等专科学校</t>
+  </si>
+  <si>
+    <t>邢台新能源职业学院</t>
+  </si>
+  <si>
+    <t>信阳科技职业学院</t>
+  </si>
+  <si>
+    <t>临沧职业学院</t>
+  </si>
+  <si>
+    <t>湘潭科技职业学院</t>
+  </si>
+  <si>
+    <t>无锡师范高等专科学校</t>
+  </si>
+  <si>
+    <t>河南新乡工商职业学院</t>
+  </si>
+  <si>
+    <t>新疆和田学院</t>
+  </si>
+  <si>
+    <t>德州工程职业学院</t>
+  </si>
+  <si>
+    <t>信阳工程职业学院</t>
+  </si>
+  <si>
+    <t>云南工业信息职业学院</t>
+  </si>
+  <si>
+    <t>怀化工商职业技术学院</t>
+  </si>
+  <si>
+    <t>周口城市职业学院</t>
+  </si>
+  <si>
+    <t>福建福耀科技大学</t>
+  </si>
+  <si>
+    <t>集美工业职业学院</t>
+  </si>
+  <si>
+    <t>安徽大学纽约石溪学院</t>
+  </si>
+  <si>
+    <t>郴州智能科技职业学院</t>
+  </si>
+  <si>
+    <t>大同数据科技职业学院</t>
+  </si>
+  <si>
+    <t>宜宾医药健康职业学院</t>
+  </si>
+  <si>
+    <t>湖北三峡航空学院</t>
+  </si>
+  <si>
+    <t>成都轨道交通职业学院</t>
+  </si>
+  <si>
+    <t>重庆现代制造职业学院</t>
+  </si>
+  <si>
+    <t>长沙科技学院</t>
+  </si>
+  <si>
+    <t>新疆工业学院</t>
+  </si>
+  <si>
+    <t>江西电子信息职业技术学院</t>
+  </si>
+  <si>
+    <t>中国人民解放军信息支援部队工程大学</t>
+  </si>
+  <si>
+    <t>鹰潭卫生职业学院</t>
+  </si>
+  <si>
+    <t>长沙科技职业学院</t>
+  </si>
+  <si>
+    <t>重庆安防职业学院</t>
+  </si>
+  <si>
+    <t>临沂城市职业学院</t>
+  </si>
+  <si>
+    <t>宁夏交通职业技术学院</t>
+  </si>
+  <si>
+    <t>成都东软学院（中外合作办学项目）</t>
+  </si>
+  <si>
+    <t>汕头大学医学院</t>
+  </si>
+  <si>
+    <t>琼台师范学院北安普顿国际学院</t>
+  </si>
+  <si>
+    <t>塔里木理工学院</t>
+  </si>
+  <si>
+    <t>大湾区大学</t>
+  </si>
+  <si>
+    <t>南通卫生健康职业学院</t>
+  </si>
+  <si>
+    <t>宜宾工业职业技术学院</t>
+  </si>
+  <si>
+    <t>上海中华职业技术学院</t>
+  </si>
+  <si>
+    <t>中国人民解放军海军士官学校</t>
+  </si>
+  <si>
+    <t>双河职业技术学院</t>
+  </si>
+  <si>
+    <t>荆门通用航空职业技术学院</t>
+  </si>
+  <si>
+    <t>西昌医学高等专科学校</t>
+  </si>
+  <si>
+    <t>乌鲁木齐职业技术学院</t>
+  </si>
+  <si>
+    <t>武警指挥学院</t>
+  </si>
+  <si>
+    <t>湖州健康职业学院</t>
+  </si>
+  <si>
+    <t>株洲科技职业学院</t>
+  </si>
+  <si>
+    <t>衡阳理工职业学院</t>
+  </si>
+  <si>
+    <t>石家庄金融职业学院</t>
+  </si>
+  <si>
+    <t>哈尔滨商贸职业学院</t>
+  </si>
+  <si>
+    <t>齐齐哈尔立德健康职业学院</t>
+  </si>
+  <si>
+    <t>常州铁道职业技术学院</t>
+  </si>
+  <si>
+    <t>苏州旅游职业学院</t>
+  </si>
+  <si>
+    <t>九江卫生健康职业学院</t>
+  </si>
+  <si>
+    <t>聊城科技职业学院</t>
+  </si>
+  <si>
+    <t>济宁汽车工程职业学院</t>
+  </si>
+  <si>
+    <t>枣庄应用技术职业学院</t>
+  </si>
+  <si>
+    <t>菏泽生物医药职业学院</t>
+  </si>
+  <si>
+    <t>岳阳科技职业学院</t>
+  </si>
+  <si>
+    <t>宁波东方理工大学</t>
+  </si>
+  <si>
+    <t>厦门大学马来西亚分校</t>
+  </si>
+  <si>
+    <t>四平现代职业学院</t>
+  </si>
+  <si>
+    <t>石家庄农林职业学院</t>
+  </si>
+  <si>
+    <t>六安应用科技职业学院</t>
+  </si>
+  <si>
+    <t>新余职业技术学院</t>
+  </si>
+  <si>
+    <t>赣州起元职业学院</t>
+  </si>
+  <si>
+    <t>赣州远恒佳职业学院</t>
+  </si>
+  <si>
+    <t>日照科技职业学院</t>
+  </si>
+  <si>
+    <t>开封工程职业学院</t>
+  </si>
+  <si>
+    <t>开封智慧健康职业学院</t>
+  </si>
+  <si>
+    <t>周口智慧能源职业学院</t>
+  </si>
+  <si>
+    <t>平顶山科技职业学院</t>
+  </si>
+  <si>
+    <t>邵阳通航职业技术学院</t>
+  </si>
+  <si>
+    <t>重庆农业职业学院</t>
+  </si>
+  <si>
+    <t>昆明航空职业学院</t>
+  </si>
+  <si>
+    <t>日喀则职业技术学院</t>
+  </si>
+  <si>
+    <t>阜康职业技术学院</t>
+  </si>
+  <si>
+    <t>海南警察学院</t>
+  </si>
+  <si>
+    <t>西安戏剧学院</t>
+  </si>
+  <si>
+    <t>新疆理工职业大学</t>
+  </si>
+  <si>
+    <t>海南洛桑旅游大学</t>
+  </si>
+  <si>
     <t>共青科技职业学院</t>
-  </si>
-  <si>
-    <t>渤海理工职业学院</t>
-  </si>
-  <si>
-    <t>白银矿冶职业技术学院</t>
-  </si>
-  <si>
-    <t>香港都会大学</t>
-  </si>
-  <si>
-    <t>香港珠海学院</t>
-  </si>
-  <si>
-    <t>江苏第二师范学院</t>
-  </si>
-  <si>
-    <t>中国科学院大学</t>
-  </si>
-  <si>
-    <t>中国人民大学（苏州校区）</t>
-  </si>
-  <si>
-    <t>甘肃卫生职业学院</t>
-  </si>
-  <si>
-    <t>兰州科技职业学院</t>
-  </si>
-  <si>
-    <t>张家口学院</t>
-  </si>
-  <si>
-    <t>山东职业学院西校区</t>
-  </si>
-  <si>
-    <t>辽宁特殊教育师范高等专科学校</t>
-  </si>
-  <si>
-    <t>四川西南航空职业学院</t>
-  </si>
-  <si>
-    <t>贵州建设职业技术学院</t>
-  </si>
-  <si>
-    <t>山东艺术设计职业学院</t>
-  </si>
-  <si>
-    <t>川南幼儿师范高等专科学校</t>
-  </si>
-  <si>
-    <t>皖北卫生职业学院</t>
-  </si>
-  <si>
-    <t>上海健康医学院</t>
-  </si>
-  <si>
-    <t>四川护理职业学院</t>
-  </si>
-  <si>
-    <t>吉安职业技术学院</t>
-  </si>
-  <si>
-    <t>温州肯恩大学</t>
-  </si>
-  <si>
-    <t>重庆资源与环境保护职业学院</t>
-  </si>
-  <si>
-    <t>成都工贸职业技术学院</t>
-  </si>
-  <si>
-    <t>香港中文大学（深圳）</t>
-  </si>
-  <si>
-    <t>成都工业职业技术学院</t>
-  </si>
-  <si>
-    <t>贵州工程职业学院</t>
-  </si>
-  <si>
-    <t>黑龙江冰雪体育职业学院</t>
-  </si>
-  <si>
-    <t>广西培贤国际职业学院</t>
-  </si>
-  <si>
-    <t>惠州城市职业学院</t>
-  </si>
-  <si>
-    <t>广州卫生职业技术学院</t>
-  </si>
-  <si>
-    <t>内蒙古民族幼儿师范高等专科学校</t>
-  </si>
-  <si>
-    <t>广东酒店管理职业技术学院</t>
-  </si>
-  <si>
-    <t>南阳农业职业学院</t>
-  </si>
-  <si>
-    <t>内蒙古艺术学院</t>
-  </si>
-  <si>
-    <t>北京网络职业学院</t>
-  </si>
-  <si>
-    <t>烟台黄金职业学院</t>
-  </si>
-  <si>
-    <t>广西金融职业技术学院</t>
-  </si>
-  <si>
-    <t>贵阳幼儿师范高等专科学校</t>
-  </si>
-  <si>
-    <t>扎兰屯职业学院</t>
-  </si>
-  <si>
-    <t>鄂尔多斯生态环境职业学院</t>
-  </si>
-  <si>
-    <t>威海海洋职业学院</t>
-  </si>
-  <si>
-    <t>湛江幼儿师范专科学校</t>
-  </si>
-  <si>
-    <t>辽宁民族师范高等专科学校</t>
-  </si>
-  <si>
-    <t>铜仁幼儿师范高等专科学校</t>
-  </si>
-  <si>
-    <t>南通师范高等专科学校</t>
-  </si>
-  <si>
-    <t>贵州工贸职业学院</t>
-  </si>
-  <si>
-    <t>贵州应用技术职业学院</t>
-  </si>
-  <si>
-    <t>贵州水利水电职业技术学院</t>
-  </si>
-  <si>
-    <t>贵州农业职业学院</t>
-  </si>
-  <si>
-    <t>毕节医学高等专科学校</t>
-  </si>
-  <si>
-    <t>广东茂名健康职业学院</t>
-  </si>
-  <si>
-    <t>广东碧桂园职业学院</t>
-  </si>
-  <si>
-    <t>广东茂名幼儿师范专科学校</t>
-  </si>
-  <si>
-    <t>广东生态工程职业学院</t>
-  </si>
-  <si>
-    <t>广东以色列理工学院</t>
-  </si>
-  <si>
-    <t>香港树仁大学</t>
-  </si>
-  <si>
-    <t>澳门城市大学</t>
-  </si>
-  <si>
-    <t>安徽公安职业学院</t>
-  </si>
-  <si>
-    <t>南昌影视传播职业学院</t>
-  </si>
-  <si>
-    <t>江西水利职业学院</t>
-  </si>
-  <si>
-    <t>深圳北理莫斯科大学</t>
-  </si>
-  <si>
-    <t>江西洪州职业学院</t>
-  </si>
-  <si>
-    <t>江西师范高等专科学校</t>
-  </si>
-  <si>
-    <t>中国社会科学院大学</t>
-  </si>
-  <si>
-    <t>哈尔滨工业大学（深圳）</t>
-  </si>
-  <si>
-    <t>阜阳幼儿师范高等专科学校</t>
-  </si>
-  <si>
-    <t>陕西机电职业技术学院</t>
-  </si>
-  <si>
-    <t>福州墨尔本理工职业学院</t>
-  </si>
-  <si>
-    <t>长春健康职业学院</t>
-  </si>
-  <si>
-    <t>浙江音乐学院</t>
-  </si>
-  <si>
-    <t>广西安全工程职业技术学院</t>
-  </si>
-  <si>
-    <t>海南体育职业技术学院</t>
-  </si>
-  <si>
-    <t>哈尔滨音乐学院</t>
-  </si>
-  <si>
-    <t>鄂尔多斯应用技术学院</t>
-  </si>
-  <si>
-    <t>滇西应用技术大学</t>
-  </si>
-  <si>
-    <t>曹妃甸职业技术学院</t>
-  </si>
-  <si>
-    <t>云南财经职业学院</t>
-  </si>
-  <si>
-    <t>贵州健康职业学院</t>
-  </si>
-  <si>
-    <t>毕节幼儿师范高等专科学校</t>
-  </si>
-  <si>
-    <t>重庆护理职业学院</t>
-  </si>
-  <si>
-    <t>三亚中瑞酒店管理职业学院</t>
-  </si>
-  <si>
-    <t>云南医药健康职业学院</t>
-  </si>
-  <si>
-    <t>茅台学院</t>
-  </si>
-  <si>
-    <t>新疆工业职业技术学院</t>
-  </si>
-  <si>
-    <t>运城师范高等专科学校</t>
-  </si>
-  <si>
-    <t>朔州师范高等专科学校</t>
-  </si>
-  <si>
-    <t>武汉铁路桥梁职业学院</t>
-  </si>
-  <si>
-    <t>青海柴达木职业技术学院</t>
-  </si>
-  <si>
-    <t>哈密职业技术学院</t>
-  </si>
-  <si>
-    <t>海南健康管理职业技术学院</t>
-  </si>
-  <si>
-    <t>深圳技术大学</t>
-  </si>
-  <si>
-    <t>中国石油大学（北京）克拉玛依校区</t>
-  </si>
-  <si>
-    <t>闽江师范高等专科学校</t>
-  </si>
-  <si>
-    <t>兰州现代职业学院</t>
-  </si>
-  <si>
-    <t>甘肃财贸职业学院</t>
-  </si>
-  <si>
-    <t>贵州电子科技职业学院</t>
-  </si>
-  <si>
-    <t>临夏现代职业学院</t>
-  </si>
-  <si>
-    <t>平凉职业技术学院</t>
-  </si>
-  <si>
-    <t>太原幼儿师范高等专科学校</t>
-  </si>
-  <si>
-    <t>湘中幼儿师范高等专科学校</t>
-  </si>
-  <si>
-    <t>贵州电子商务职业技术学院</t>
-  </si>
-  <si>
-    <t>贵州护理职业技术学院</t>
-  </si>
-  <si>
-    <t>贵州食品工程职业学院</t>
-  </si>
-  <si>
-    <t>贵州装备制造职业学院</t>
-  </si>
-  <si>
-    <t>黔南民族幼儿师范高等专科学校</t>
-  </si>
-  <si>
-    <t>贵州经贸职业技术学院</t>
-  </si>
-  <si>
-    <t>青海高等职业技术学院</t>
-  </si>
-  <si>
-    <t>吐鲁番职业技术学院</t>
-  </si>
-  <si>
-    <t>博尔塔拉职业技术学院</t>
-  </si>
-  <si>
-    <t>新疆生产建设兵团兴新职业技术学院</t>
-  </si>
-  <si>
-    <t>昭通卫生职业学院</t>
-  </si>
-  <si>
-    <t>云南交通运输职业学院</t>
-  </si>
-  <si>
-    <t>昆明铁道职业技术学院</t>
-  </si>
-  <si>
-    <t>大理护理职业学院</t>
-  </si>
-  <si>
-    <t>云南水利水电职业学院</t>
-  </si>
-  <si>
-    <t>宜春幼儿师范高等专科学校</t>
-  </si>
-  <si>
-    <t>广东江门中医药职业学院</t>
-  </si>
-  <si>
-    <t>惠州工程职业学院</t>
-  </si>
-  <si>
-    <t>长春师范高等专科学校</t>
-  </si>
-  <si>
-    <t>吉林水利电力职业学院</t>
-  </si>
-  <si>
-    <t>天津体育职业学院</t>
-  </si>
-  <si>
-    <t>天津滨海汽车工程职业学院</t>
-  </si>
-  <si>
-    <t>石家庄城市经济职业学院</t>
-  </si>
-  <si>
-    <t>唐山幼儿师范高等专科学校</t>
-  </si>
-  <si>
-    <t>吉林职业技术学院</t>
-  </si>
-  <si>
-    <t>泉州工程职业技术学院</t>
-  </si>
-  <si>
-    <t>四川应用技术职业学院</t>
-  </si>
-  <si>
-    <t>西藏农牧学院</t>
-  </si>
-  <si>
-    <t>贵州航空职业技术学院</t>
-  </si>
-  <si>
-    <t>华北理工大学冀唐学院</t>
-  </si>
-  <si>
-    <t>浙江特殊教育职业学院</t>
-  </si>
-  <si>
-    <t>浙江安防职业技术学院</t>
-  </si>
-  <si>
-    <t>浙江舟山群岛新区旅游与健康职业学院</t>
-  </si>
-  <si>
-    <t>红河卫生职业学院</t>
-  </si>
-  <si>
-    <t>大理农林职业技术学院</t>
-  </si>
-  <si>
-    <t>云南特殊教育职业学院</t>
-  </si>
-  <si>
-    <t>吕梁职业技术学院</t>
-  </si>
-  <si>
-    <t>菏泽职业学院</t>
-  </si>
-  <si>
-    <t>山东特殊教育职业学院</t>
-  </si>
-  <si>
-    <t>日照航海工程职业学院</t>
-  </si>
-  <si>
-    <t>西宁城市职业技术学院</t>
-  </si>
-  <si>
-    <t>江西卫生职业学院</t>
-  </si>
-  <si>
-    <t>江西医学高等专科学校</t>
-  </si>
-  <si>
-    <t>赣南卫生健康职业学院</t>
-  </si>
-  <si>
-    <t>大连理工大学盘锦校区</t>
-  </si>
-  <si>
-    <t>无锡职业技术大学</t>
-  </si>
-  <si>
-    <t>苏州工业园区服务外包职业学院</t>
-  </si>
-  <si>
-    <t>江苏财会职业学院</t>
-  </si>
-  <si>
-    <t>南京审计大学金审学院</t>
-  </si>
-  <si>
-    <t>昆山杜克大学</t>
-  </si>
-  <si>
-    <t>盐城幼儿师范高等专科学校</t>
-  </si>
-  <si>
-    <t>苏州幼儿师范高等专科学校</t>
-  </si>
-  <si>
-    <t>江苏城乡建设职业学院</t>
-  </si>
-  <si>
-    <t>江苏安全技术职业学院</t>
-  </si>
-  <si>
-    <t>江苏旅游职业学院</t>
-  </si>
-  <si>
-    <t>湖南幼儿师范高等专科学校</t>
-  </si>
-  <si>
-    <t>湖南财经工业职业技术学院</t>
-  </si>
-  <si>
-    <t>湘南幼儿师范高等专科学校</t>
-  </si>
-  <si>
-    <t>武汉光谷职业学院</t>
-  </si>
-  <si>
-    <t>湖北幼儿师范高等专科学校</t>
-  </si>
-  <si>
-    <t>湖北铁道运输职业学院</t>
-  </si>
-  <si>
-    <t>武汉海事职业学院</t>
-  </si>
-  <si>
-    <t>长江艺术工程职业学院</t>
-  </si>
-  <si>
-    <t>荆门职业学院</t>
-  </si>
-  <si>
-    <t>黑龙江公安警官职业学院</t>
-  </si>
-  <si>
-    <t>河南应用技术职业学院</t>
-  </si>
-  <si>
-    <t>郑州信息工程职业学院</t>
-  </si>
-  <si>
-    <t>河南林业职业学院</t>
-  </si>
-  <si>
-    <t>濮阳医学高等专科学校</t>
-  </si>
-  <si>
-    <t>河南轻工职业学院</t>
-  </si>
-  <si>
-    <t>驻马店幼儿师范高等专科学校</t>
-  </si>
-  <si>
-    <t>郑州财税金融职业学院</t>
-  </si>
-  <si>
-    <t>三门峡社会管理职业学院</t>
-  </si>
-  <si>
-    <t>河南测绘职业学院</t>
-  </si>
-  <si>
-    <t>鹤壁能源化工职业学院</t>
-  </si>
-  <si>
-    <t>平顶山文化艺术职业学院</t>
-  </si>
-  <si>
-    <t>保定幼儿师范高等专科学校</t>
-  </si>
-  <si>
-    <t>河北工艺美术职业学院</t>
-  </si>
-  <si>
-    <t>衡水职业技术学院</t>
-  </si>
-  <si>
-    <t>新疆科技职业技术学院</t>
-  </si>
-  <si>
-    <t>巴中职业技术学院</t>
-  </si>
-  <si>
-    <t>上海公安学院</t>
-  </si>
-  <si>
-    <t>阳泉职业技术学院</t>
-  </si>
-  <si>
-    <t>宁夏幼儿师范高等专科学校</t>
-  </si>
-  <si>
-    <t>宁夏艺术职业学院</t>
-  </si>
-  <si>
-    <t>宁夏体育职业学院</t>
-  </si>
-  <si>
-    <t>沈阳化工大学</t>
-  </si>
-  <si>
-    <t>沈阳理工大学</t>
-  </si>
-  <si>
-    <t>辽宁税务高等专科学校</t>
-  </si>
-  <si>
-    <t>上饶幼儿师范高等专科学校</t>
-  </si>
-  <si>
-    <t>抚州幼儿师范高等专科学校</t>
-  </si>
-  <si>
-    <t>江苏联合职业技术学院</t>
-  </si>
-  <si>
-    <t>扬州中瑞酒店职业学院</t>
-  </si>
-  <si>
-    <t>江苏航空职业技术学院</t>
-  </si>
-  <si>
-    <t>湖南工商职业学院</t>
-  </si>
-  <si>
-    <t>湖南吉利汽车职业技术学院</t>
-  </si>
-  <si>
-    <t>湖南劳动人事职业学院</t>
-  </si>
-  <si>
-    <t>湖北职业技术学院</t>
-  </si>
-  <si>
-    <t>天府新区信息职业学院</t>
-  </si>
-  <si>
-    <t>天府新区通用航空职业学院</t>
-  </si>
-  <si>
-    <t>辽宁生态工程职业学院</t>
-  </si>
-  <si>
-    <t>桂林生命与健康职业技术学院</t>
-  </si>
-  <si>
-    <t>江阳城建职业学院</t>
-  </si>
-  <si>
-    <t>承德应用技术职业学院</t>
-  </si>
-  <si>
-    <t>哈尔滨北方航空职业技术学院</t>
-  </si>
-  <si>
-    <t>广元中核职业技术学院</t>
-  </si>
-  <si>
-    <t>南昌大学抚州医学院</t>
-  </si>
-  <si>
-    <t>郑州西亚斯学院</t>
-  </si>
-  <si>
-    <t>石河子工程职业技术学院</t>
-  </si>
-  <si>
-    <t>资阳口腔职业学院</t>
-  </si>
-  <si>
-    <t>眉山药科职业学院</t>
-  </si>
-  <si>
-    <t>神木职业技术学院</t>
-  </si>
-  <si>
-    <t>西安健康工程职业学院</t>
-  </si>
-  <si>
-    <t>福建技术师范学院</t>
-  </si>
-  <si>
-    <t>西昌民族幼儿师范高等专科学校</t>
-  </si>
-  <si>
-    <t>达州中医药职业学院</t>
-  </si>
-  <si>
-    <t>赣州职业技术学院</t>
-  </si>
-  <si>
-    <t>中国消防救援学院</t>
-  </si>
-  <si>
-    <t>海南卫生健康职业学院</t>
-  </si>
-  <si>
-    <t>西南财经大学特拉华数据科学学院</t>
-  </si>
-  <si>
-    <t>毕节工业职业技术学院</t>
-  </si>
-  <si>
-    <t>大同师范高等专科学校</t>
-  </si>
-  <si>
-    <t>云南工贸职业技术学院</t>
-  </si>
-  <si>
-    <t>云南理工职业学院</t>
-  </si>
-  <si>
-    <t>云南轻纺职业学院</t>
-  </si>
-  <si>
-    <t>信阳航空职业学院</t>
-  </si>
-  <si>
-    <t>六盘水幼儿师范高等专科学校</t>
-  </si>
-  <si>
-    <t>内江卫生与健康职业学院</t>
-  </si>
-  <si>
-    <t>南充科技职业学院</t>
-  </si>
-  <si>
-    <t>四川体育职业学院</t>
-  </si>
-  <si>
-    <t>天府新区航空旅游职业学院</t>
-  </si>
-  <si>
-    <t>安徽艺术学院</t>
-  </si>
-  <si>
-    <t>宝鸡三和职业学院</t>
-  </si>
-  <si>
-    <t>广东江门幼儿师范高等专科学校</t>
-  </si>
-  <si>
-    <t>广东茂名农林科技职业学院</t>
-  </si>
-  <si>
-    <t>广东财贸职业学院</t>
-  </si>
-  <si>
-    <t>广西自然资源职业技术学院</t>
-  </si>
-  <si>
-    <t>广西蓝天航空职业学院</t>
-  </si>
-  <si>
-    <t>德阳城市轨道交通职业学院</t>
-  </si>
-  <si>
-    <t>德阳科贸职业学院</t>
-  </si>
-  <si>
-    <t>怀化师范高等专科学校</t>
-  </si>
-  <si>
-    <t>攀枝花攀西职业学院</t>
-  </si>
-  <si>
-    <t>新疆科信职业技术学院</t>
-  </si>
-  <si>
-    <t>曲靖职业技术学院</t>
-  </si>
-  <si>
-    <t>江西婺源茶业职业学院</t>
-  </si>
-  <si>
-    <t>江西软件职业技术大学</t>
-  </si>
-  <si>
-    <t>河南地矿职业学院</t>
-  </si>
-  <si>
-    <t>河南物流职业学院</t>
-  </si>
-  <si>
-    <t>玉柴职业技术学院</t>
-  </si>
-  <si>
-    <t>萍乡卫生职业学院</t>
-  </si>
-  <si>
-    <t>西湖大学</t>
-  </si>
-  <si>
-    <t>资阳环境科技职业学院</t>
-  </si>
-  <si>
-    <t>郑州亚欧交通职业学院</t>
-  </si>
-  <si>
-    <t>郑州卫生健康职业学院</t>
-  </si>
-  <si>
-    <t>阿坝职业学院</t>
-  </si>
-  <si>
-    <t>重庆健康职业学院</t>
-  </si>
-  <si>
-    <t>昆明幼儿师范高等专科学校</t>
-  </si>
-  <si>
-    <t>江西管理职业学院</t>
-  </si>
-  <si>
-    <t>铁门关职业技术学院</t>
-  </si>
-  <si>
-    <t>克孜勒苏职业技术学院</t>
-  </si>
-  <si>
-    <t>和田职业技术学院</t>
-  </si>
-  <si>
-    <t>公安消防部队高等专科学校</t>
-  </si>
-  <si>
-    <t>青岛工程职业学院</t>
-  </si>
-  <si>
-    <t>株洲师范高等专科学校</t>
-  </si>
-  <si>
-    <t>邯郸幼儿师范高等专科学校</t>
-  </si>
-  <si>
-    <t>贵州机电职业技术学院</t>
-  </si>
-  <si>
-    <t>贵州财经职业学院</t>
-  </si>
-  <si>
-    <t>贵州民用航空职业学院</t>
-  </si>
-  <si>
-    <t>重庆智能工程职业学院</t>
-  </si>
-  <si>
-    <t>重庆理工职业学院</t>
-  </si>
-  <si>
-    <t>九江理工职业学院</t>
-  </si>
-  <si>
-    <t>长春早期教育职业学院</t>
-  </si>
-  <si>
-    <t>黄山健康职业学院</t>
-  </si>
-  <si>
-    <t>南充电影工业职业学院</t>
-  </si>
-  <si>
-    <t>鞍山职业技术学院</t>
-  </si>
-  <si>
-    <t>浙江宇翔职业技术学院</t>
-  </si>
-  <si>
-    <t>南昌健康职业技术学院</t>
-  </si>
-  <si>
-    <t>青岛航空科技职业学院</t>
-  </si>
-  <si>
-    <t>永州师范高等专科学校</t>
-  </si>
-  <si>
-    <t>林州建筑职业技术学院</t>
-  </si>
-  <si>
-    <t>广西制造工程职业技术学院</t>
-  </si>
-  <si>
-    <t>河南女子职业学院</t>
-  </si>
-  <si>
-    <t>南阳科技职业学院</t>
-  </si>
-  <si>
-    <t>潍坊环境工程职业学院</t>
-  </si>
-  <si>
-    <t>河南对外经济贸易职业学院</t>
-  </si>
-  <si>
-    <t>绵阳飞行职业学院</t>
-  </si>
-  <si>
-    <t>梅河口康美职业技术学院</t>
-  </si>
-  <si>
-    <t>长沙幼儿师范高等专科学校</t>
-  </si>
-  <si>
-    <t>邯郸科技职业学院</t>
-  </si>
-  <si>
-    <t>烟台文化旅游职业学院</t>
-  </si>
-  <si>
-    <t>复旦大学上海医学院</t>
-  </si>
-  <si>
-    <t>合肥工业大学宣城校区</t>
-  </si>
-  <si>
-    <t>赤峰应用技术职业学院</t>
-  </si>
-  <si>
-    <t>衡阳幼儿师范高等专科学校</t>
-  </si>
-  <si>
-    <t>榆林能源科技职业学院</t>
-  </si>
-  <si>
-    <t>培黎职业学院</t>
-  </si>
-  <si>
-    <t>石嘴山工贸职业技术学院</t>
-  </si>
-  <si>
-    <t>德阳农业科技职业学院</t>
-  </si>
-  <si>
-    <t>南充文化旅游职业学院</t>
-  </si>
-  <si>
-    <t>广西物流职业技术学院</t>
-  </si>
-  <si>
-    <t>湖北健康职业学院</t>
-  </si>
-  <si>
-    <t>郑州体育职业学院</t>
-  </si>
-  <si>
-    <t>汝州职业技术学院</t>
-  </si>
-  <si>
-    <t>兰考三农职业学院</t>
-  </si>
-  <si>
-    <t>濮阳石油化工职业技术学院</t>
-  </si>
-  <si>
-    <t>临沂科技职业学院</t>
-  </si>
-  <si>
-    <t>朔州陶瓷职业技术学院</t>
-  </si>
-  <si>
-    <t>唐山海运职业学院</t>
-  </si>
-  <si>
-    <t>梧州医学高等专科学校</t>
-  </si>
-  <si>
-    <t>钦州幼儿师范高等专科学校</t>
-  </si>
-  <si>
-    <t>江苏海洋大学</t>
-  </si>
-  <si>
-    <t>辽宁师范高等专科学校</t>
-  </si>
-  <si>
-    <t>浙江警察学院</t>
-  </si>
-  <si>
-    <t>云南中医药大学</t>
-  </si>
-  <si>
-    <t>烟台幼儿师范高等专科学校</t>
-  </si>
-  <si>
-    <t>广州幼儿师范高等专科学校</t>
-  </si>
-  <si>
-    <t>中国人民解放军陆军步兵学院</t>
-  </si>
-  <si>
-    <t>中国人民解放军陆军特种作战学院</t>
-  </si>
-  <si>
-    <t>中国人民解放军陆军边海防学院</t>
-  </si>
-  <si>
-    <t>重庆移通学院德国工程学院</t>
-  </si>
-  <si>
-    <t>香港恒生大学</t>
-  </si>
-  <si>
-    <t>邢台应用技术职业学院</t>
-  </si>
-  <si>
-    <t>吉林通用航空职业技术学院</t>
-  </si>
-  <si>
-    <t>通化医药健康职业学院</t>
-  </si>
-  <si>
-    <t>上海南湖职业技术学院</t>
-  </si>
-  <si>
-    <t>浙江金华科贸职业技术学院</t>
-  </si>
-  <si>
-    <t>宿州航空职业学院</t>
-  </si>
-  <si>
-    <t>和君职业学院</t>
-  </si>
-  <si>
-    <t>湖北孝感美珈职业学院</t>
-  </si>
-  <si>
-    <t>广东梅州职业技术学院</t>
-  </si>
-  <si>
-    <t>广东潮州卫生健康职业学院</t>
-  </si>
-  <si>
-    <t>广东云浮中医药职业学院</t>
-  </si>
-  <si>
-    <t>防城港职业技术学院</t>
-  </si>
-  <si>
-    <t>广西信息职业技术学院</t>
-  </si>
-  <si>
-    <t>广西农业工程职业技术学院</t>
-  </si>
-  <si>
-    <t>北海康养职业学院</t>
-  </si>
-  <si>
-    <t>甘孜职业学院</t>
-  </si>
-  <si>
-    <t>贵州文化旅游职业学院</t>
-  </si>
-  <si>
-    <t>自贡职业技术学院</t>
-  </si>
-  <si>
-    <t>宝鸡中北职业学院</t>
-  </si>
-  <si>
-    <t>兰州航空职业技术学院</t>
-  </si>
-  <si>
-    <t>白银希望职业技术学院</t>
-  </si>
-  <si>
-    <t>滨州科技职业学院</t>
-  </si>
-  <si>
-    <t>重庆工信职业学院</t>
-  </si>
-  <si>
-    <t>郑州医药健康职业学院</t>
-  </si>
-  <si>
-    <t>郑州城建职业学院</t>
-  </si>
-  <si>
-    <t>信阳艺术职业学院</t>
-  </si>
-  <si>
-    <t>周口文理职业学院</t>
-  </si>
-  <si>
-    <t>洛阳文化旅游职业学院</t>
-  </si>
-  <si>
-    <t>长治幼儿师范高等专科学校</t>
-  </si>
-  <si>
-    <t>红河职业技术学院</t>
-  </si>
-  <si>
-    <t>塔城职业技术学院</t>
-  </si>
-  <si>
-    <t>塔里木职业技术学院</t>
-  </si>
-  <si>
-    <t>泸州医疗器械职业学院</t>
-  </si>
-  <si>
-    <t>郑州轨道工程职业学院</t>
-  </si>
-  <si>
-    <t>郑州电子商务职业学院</t>
-  </si>
-  <si>
-    <t>山西通用航空职业技术学院</t>
-  </si>
-  <si>
-    <t>青岛幼儿师范高等专科学校</t>
-  </si>
-  <si>
-    <t>阿勒泰职业技术学院</t>
-  </si>
-  <si>
-    <t>喀什职业技术学院</t>
-  </si>
-  <si>
-    <t>浙江大学医学院</t>
-  </si>
-  <si>
-    <t>解放军国际关系学院</t>
-  </si>
-  <si>
-    <t>中国人民解放军西安通信学院</t>
-  </si>
-  <si>
-    <t>解放军陆军航空兵学院</t>
-  </si>
-  <si>
-    <t>西藏警官高等专科学校</t>
-  </si>
-  <si>
-    <t>空军勤务学院</t>
-  </si>
-  <si>
-    <t>中国人民解放军海军大连舰艇学院</t>
-  </si>
-  <si>
-    <t>海军工程大学</t>
-  </si>
-  <si>
-    <t>空军航空大学</t>
-  </si>
-  <si>
-    <t>解放军电子工程学院</t>
-  </si>
-  <si>
-    <t>陆军兵种大学</t>
-  </si>
-  <si>
-    <t>解放军南京陆军指挥学院</t>
-  </si>
-  <si>
-    <t>解放军工程兵学院</t>
-  </si>
-  <si>
-    <t>空军指挥学院</t>
-  </si>
-  <si>
-    <t>解放军空军第一航空学院</t>
-  </si>
-  <si>
-    <t>解放军空军西安飞行学院</t>
-  </si>
-  <si>
-    <t>解放军装甲兵学院</t>
-  </si>
-  <si>
-    <t>解放军装甲兵技术学院</t>
-  </si>
-  <si>
-    <t>海军指挥学院</t>
-  </si>
-  <si>
-    <t>广东汕头幼儿师范高等专科学校</t>
-  </si>
-  <si>
-    <t>西南大学西塔学院</t>
-  </si>
-  <si>
-    <t>重庆医科大学国际医学院</t>
-  </si>
-  <si>
-    <t>广东肇庆航空职业学院</t>
-  </si>
-  <si>
-    <t>重庆五一职业技术学院</t>
-  </si>
-  <si>
-    <t>益阳师范高等专科学校</t>
-  </si>
-  <si>
-    <t>贵州大学北阿拉巴马国际工程技术学院</t>
-  </si>
-  <si>
-    <t>常州幼儿师范高等专科学校</t>
-  </si>
-  <si>
-    <t>娄底幼儿师范高等专科学校</t>
-  </si>
-  <si>
-    <t>吕梁师范高等专科学校</t>
-  </si>
-  <si>
-    <t>上海科创职业技术学院</t>
-  </si>
-  <si>
-    <t>上海闵行职业技术学院</t>
-  </si>
-  <si>
-    <t>上海现代化工职业学院</t>
-  </si>
-  <si>
-    <t>上海建设管理职业技术学院</t>
-  </si>
-  <si>
-    <t>玉溪职业技术学院</t>
-  </si>
-  <si>
-    <t>保山职业学院</t>
-  </si>
-  <si>
-    <t>昭通职业学院</t>
-  </si>
-  <si>
-    <t>重庆中医药学院</t>
-  </si>
-  <si>
-    <t>郑州汽车工程职业学院</t>
-  </si>
-  <si>
-    <t>周口理工职业学院</t>
-  </si>
-  <si>
-    <t>秦皇岛工业职业技术学院</t>
-  </si>
-  <si>
-    <t>广西质量工程职业技术学院</t>
-  </si>
-  <si>
-    <t>潍坊食品科技职业学院</t>
-  </si>
-  <si>
-    <t>贵州铜仁数据职业学院</t>
-  </si>
-  <si>
-    <t>新星职业技术学院</t>
-  </si>
-  <si>
-    <t>上饶卫生健康职业学院</t>
-  </si>
-  <si>
-    <t>可克达拉职业技术学院</t>
-  </si>
-  <si>
-    <t>海南比勒费尔德应用科学大学</t>
-  </si>
-  <si>
-    <t>图木舒克职业技术学院</t>
-  </si>
-  <si>
-    <t>贵州体育职业学院</t>
-  </si>
-  <si>
-    <t>新疆司法警官职业学院</t>
-  </si>
-  <si>
-    <t>郑州美术学院</t>
-  </si>
-  <si>
-    <t>衡水健康科技职业学院</t>
-  </si>
-  <si>
-    <t>沧州航空职业学院</t>
-  </si>
-  <si>
-    <t>邯郸应用技术职业学院</t>
-  </si>
-  <si>
-    <t>山东城市服务职业学院</t>
-  </si>
-  <si>
-    <t>南阳工艺美术职业学院</t>
-  </si>
-  <si>
-    <t>濮阳科技职业学院</t>
-  </si>
-  <si>
-    <t>开封职业学院</t>
-  </si>
-  <si>
-    <t>郑州软件职业技术学院</t>
-  </si>
-  <si>
-    <t>郑州智能科技职业学院</t>
-  </si>
-  <si>
-    <t>襄阳科技职业学院</t>
-  </si>
-  <si>
-    <t>宜昌科技职业学院</t>
-  </si>
-  <si>
-    <t>邵阳工业职业技术学院</t>
-  </si>
-  <si>
-    <t>长沙轨道交通职业学院</t>
-  </si>
-  <si>
-    <t>岳阳现代服务职业学院</t>
-  </si>
-  <si>
-    <t>衡阳科技职业学院</t>
-  </si>
-  <si>
-    <t>香港科技大学（广州）</t>
-  </si>
-  <si>
-    <t>珠海格力职业学院</t>
-  </si>
-  <si>
-    <t>丽江职业技术学院</t>
-  </si>
-  <si>
-    <t>遂宁能源职业学院</t>
-  </si>
-  <si>
-    <t>遂宁工程职业学院</t>
-  </si>
-  <si>
-    <t>遂宁职业学院</t>
-  </si>
-  <si>
-    <t>文山职业技术学院</t>
-  </si>
-  <si>
-    <t>香格里拉职业学院</t>
-  </si>
-  <si>
-    <t>定西职业技术学院</t>
-  </si>
-  <si>
-    <t>宁夏卫生健康职业技术学院</t>
-  </si>
-  <si>
-    <t>阿克苏工业职业技术学院</t>
-  </si>
-  <si>
-    <t>喀什理工职业技术学院</t>
-  </si>
-  <si>
-    <t>昆玉职业技术学院</t>
-  </si>
-  <si>
-    <t>长沙文创艺术职业学院</t>
-  </si>
-  <si>
-    <t>洛阳商业职业学院</t>
-  </si>
-  <si>
-    <t>常德科技职业技术学院</t>
-  </si>
-  <si>
-    <t>桂林信息工程职业学院</t>
-  </si>
-  <si>
-    <t>郴州思科职业学院</t>
-  </si>
-  <si>
-    <t>重庆数字产业职业技术学院</t>
-  </si>
-  <si>
-    <t>长春数字科技职业学院</t>
-  </si>
-  <si>
-    <t>烟台城市科技职业学院</t>
-  </si>
-  <si>
-    <t>吉安幼儿师范高等专科学校</t>
-  </si>
-  <si>
-    <t>香港城市大学（东莞）</t>
-  </si>
-  <si>
-    <t>安徽公安学院</t>
-  </si>
-  <si>
-    <t>中国人民武装警察部队特种警察学院</t>
-  </si>
-  <si>
-    <t>海军勤务学院</t>
-  </si>
-  <si>
-    <t>山东文化艺术职业学院</t>
-  </si>
-  <si>
-    <t>日照康养职业学院</t>
-  </si>
-  <si>
-    <t>烟台卫生健康职业学院</t>
-  </si>
-  <si>
-    <t>贵州传媒职业学院</t>
-  </si>
-  <si>
-    <t>江苏司法警官职业学院</t>
-  </si>
-  <si>
-    <t>蚌埠城市轨道交通职业学院</t>
-  </si>
-  <si>
-    <t>海南东方新丝路职业学院</t>
-  </si>
-  <si>
-    <t>贵州生态能源职业学院</t>
-  </si>
-  <si>
-    <t>黔东南理工职业学院</t>
-  </si>
-  <si>
-    <t>康复大学</t>
-  </si>
-  <si>
-    <t>深圳理工大学</t>
-  </si>
-  <si>
-    <t>商丘幼儿师范高等专科学校</t>
-  </si>
-  <si>
-    <t>华北水利水电大学乌拉尔学院</t>
-  </si>
-  <si>
-    <t>郑州食品工程职业学院</t>
-  </si>
-  <si>
-    <t>焦作新材料职业学院</t>
-  </si>
-  <si>
-    <t>江西樟树中医药职业学院</t>
-  </si>
-  <si>
-    <t>海南医科大学西英格兰学院</t>
-  </si>
-  <si>
-    <t>青海理工学院</t>
-  </si>
-  <si>
-    <t>赣东职业技术学院</t>
-  </si>
-  <si>
-    <t>河南体育学院</t>
-  </si>
-  <si>
-    <t>芜湖航空职业学院</t>
-  </si>
-  <si>
-    <t>上海浦东职业技术学院</t>
-  </si>
-  <si>
-    <t>芜湖医药健康职业学院</t>
-  </si>
-  <si>
-    <t>怒江职业技术学院</t>
-  </si>
-  <si>
-    <t>长沙医药健康职业学院</t>
-  </si>
-  <si>
-    <t>海南艺术职业学院</t>
-  </si>
-  <si>
-    <t>玉林职业技术学院</t>
-  </si>
-  <si>
-    <t>海口旅游职业学院</t>
-  </si>
-  <si>
-    <t>三亚护理职业学院</t>
-  </si>
-  <si>
-    <t>广西智能制造职业技术学院</t>
-  </si>
-  <si>
-    <t>深圳城市职业学院</t>
-  </si>
-  <si>
-    <t>盐城农业科技职业学院</t>
-  </si>
-  <si>
-    <t>驻马店农业工程职业学院</t>
-  </si>
-  <si>
-    <t>宿迁幼儿师范高等专科学校</t>
-  </si>
-  <si>
-    <t>邢台新能源职业学院</t>
-  </si>
-  <si>
-    <t>信阳科技职业学院</t>
-  </si>
-  <si>
-    <t>临沧职业学院</t>
-  </si>
-  <si>
-    <t>湘潭科技职业学院</t>
-  </si>
-  <si>
-    <t>无锡师范高等专科学校</t>
-  </si>
-  <si>
-    <t>河南新乡工商职业学院</t>
-  </si>
-  <si>
-    <t>新疆和田学院</t>
-  </si>
-  <si>
-    <t>德州工程职业学院</t>
-  </si>
-  <si>
-    <t>信阳工程职业学院</t>
-  </si>
-  <si>
-    <t>云南工业信息职业学院</t>
-  </si>
-  <si>
-    <t>怀化工商职业技术学院</t>
-  </si>
-  <si>
-    <t>周口城市职业学院</t>
-  </si>
-  <si>
-    <t>福建福耀科技大学</t>
-  </si>
-  <si>
-    <t>集美工业职业学院</t>
-  </si>
-  <si>
-    <t>安徽大学纽约石溪学院</t>
-  </si>
-  <si>
-    <t>郴州智能科技职业学院</t>
-  </si>
-  <si>
-    <t>大同数据科技职业学院</t>
-  </si>
-  <si>
-    <t>宜宾医药健康职业学院</t>
-  </si>
-  <si>
-    <t>湖北三峡航空学院</t>
-  </si>
-  <si>
-    <t>成都轨道交通职业学院</t>
-  </si>
-  <si>
-    <t>重庆现代制造职业学院</t>
-  </si>
-  <si>
-    <t>长沙科技学院</t>
-  </si>
-  <si>
-    <t>新疆工业学院</t>
-  </si>
-  <si>
-    <t>江西电子信息职业技术学院</t>
-  </si>
-  <si>
-    <t>中国人民解放军信息支援部队工程大学</t>
-  </si>
-  <si>
-    <t>鹰潭卫生职业学院</t>
-  </si>
-  <si>
-    <t>长沙科技职业学院</t>
-  </si>
-  <si>
-    <t>重庆安防职业学院</t>
-  </si>
-  <si>
-    <t>临沂城市职业学院</t>
-  </si>
-  <si>
-    <t>宁夏交通职业技术学院</t>
-  </si>
-  <si>
-    <t>成都东软学院（中外合作办学项目）</t>
-  </si>
-  <si>
-    <t>武警指挥学院</t>
-  </si>
-  <si>
-    <t>厦门大学马来西亚分校</t>
-  </si>
-  <si>
-    <t>中国人民解放军海军士官学校</t>
-  </si>
-  <si>
-    <t>双河职业技术学院</t>
-  </si>
-  <si>
-    <t>荆门通用航空职业技术学院</t>
-  </si>
-  <si>
-    <t>西昌医学高等专科学校</t>
-  </si>
-  <si>
-    <t>乌鲁木齐职业技术学院</t>
-  </si>
-  <si>
-    <t>株洲科技职业学院</t>
-  </si>
-  <si>
-    <t>衡阳理工职业学院</t>
-  </si>
-  <si>
-    <t>宜宾工业职业技术学院</t>
-  </si>
-  <si>
-    <t>南通卫生健康职业学院</t>
-  </si>
-  <si>
-    <t>四平现代职业学院</t>
-  </si>
-  <si>
-    <t>琼台师范学院北安普顿国际学院</t>
-  </si>
-  <si>
-    <t>石家庄金融职业学院</t>
-  </si>
-  <si>
-    <t>石家庄农林职业学院</t>
-  </si>
-  <si>
-    <t>哈尔滨商贸职业学院</t>
-  </si>
-  <si>
-    <t>齐齐哈尔立德健康职业学院</t>
-  </si>
-  <si>
-    <t>常州铁道职业技术学院</t>
-  </si>
-  <si>
-    <t>苏州旅游职业学院</t>
-  </si>
-  <si>
-    <t>湖州健康职业学院</t>
-  </si>
-  <si>
-    <t>六安应用科技职业学院</t>
-  </si>
-  <si>
-    <t>九江卫生健康职业学院</t>
-  </si>
-  <si>
-    <t>新余职业技术学院</t>
-  </si>
-  <si>
-    <t>赣州起元职业学院</t>
-  </si>
-  <si>
-    <t>赣州远恒佳职业学院</t>
-  </si>
-  <si>
-    <t>聊城科技职业学院</t>
-  </si>
-  <si>
-    <t>济宁汽车工程职业学院</t>
-  </si>
-  <si>
-    <t>日照科技职业学院</t>
-  </si>
-  <si>
-    <t>枣庄应用技术职业学院</t>
-  </si>
-  <si>
-    <t>菏泽生物医药职业学院</t>
-  </si>
-  <si>
-    <t>开封工程职业学院</t>
-  </si>
-  <si>
-    <t>开封智慧健康职业学院</t>
-  </si>
-  <si>
-    <t>周口智慧能源职业学院</t>
-  </si>
-  <si>
-    <t>平顶山科技职业学院</t>
-  </si>
-  <si>
-    <t>岳阳科技职业学院</t>
-  </si>
-  <si>
-    <t>邵阳通航职业技术学院</t>
-  </si>
-  <si>
-    <t>重庆农业职业学院</t>
-  </si>
-  <si>
-    <t>昆明航空职业学院</t>
-  </si>
-  <si>
-    <t>日喀则职业技术学院</t>
-  </si>
-  <si>
-    <t>阜康职业技术学院</t>
   </si>
 </sst>
 </file>
@@ -9012,11 +8985,17 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -9474,31 +9453,28 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -9507,120 +9483,124 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -9680,13 +9660,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/customStorage/customStorage.xml><?xml version="1.0" encoding="utf-8"?>
-<customStorage xmlns="https://web.wps.cn/et/2018/main">
-  <book/>
-  <sheets/>
-</customStorage>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -9976,10 +9949,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:A2992"/>
+  <dimension ref="A1:A2983"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="1" max="1" width="38.8888888888889" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
@@ -22679,97 +22652,97 @@
     </row>
     <row r="2540" spans="1:1">
       <c r="A2540" t="s">
-        <v>2539</v>
+        <v>661</v>
       </c>
     </row>
     <row r="2541" spans="1:1">
       <c r="A2541" t="s">
-        <v>2540</v>
+        <v>2539</v>
       </c>
     </row>
     <row r="2542" spans="1:1">
       <c r="A2542" t="s">
-        <v>2541</v>
+        <v>2540</v>
       </c>
     </row>
     <row r="2543" spans="1:1">
       <c r="A2543" t="s">
-        <v>2542</v>
+        <v>2541</v>
       </c>
     </row>
     <row r="2544" spans="1:1">
       <c r="A2544" t="s">
-        <v>2543</v>
+        <v>2542</v>
       </c>
     </row>
     <row r="2545" spans="1:1">
       <c r="A2545" t="s">
-        <v>2544</v>
+        <v>2543</v>
       </c>
     </row>
     <row r="2546" spans="1:1">
       <c r="A2546" t="s">
-        <v>2545</v>
+        <v>2544</v>
       </c>
     </row>
     <row r="2547" spans="1:1">
       <c r="A2547" t="s">
-        <v>2546</v>
+        <v>2545</v>
       </c>
     </row>
     <row r="2548" spans="1:1">
       <c r="A2548" t="s">
-        <v>2547</v>
+        <v>2546</v>
       </c>
     </row>
     <row r="2549" spans="1:1">
       <c r="A2549" t="s">
-        <v>2548</v>
+        <v>2547</v>
       </c>
     </row>
     <row r="2550" spans="1:1">
       <c r="A2550" t="s">
-        <v>2549</v>
+        <v>2548</v>
       </c>
     </row>
     <row r="2551" spans="1:1">
       <c r="A2551" t="s">
-        <v>2550</v>
+        <v>2549</v>
       </c>
     </row>
     <row r="2552" spans="1:1">
       <c r="A2552" t="s">
-        <v>2551</v>
+        <v>2550</v>
       </c>
     </row>
     <row r="2553" spans="1:1">
       <c r="A2553" t="s">
-        <v>2552</v>
+        <v>2551</v>
       </c>
     </row>
     <row r="2554" spans="1:1">
       <c r="A2554" t="s">
-        <v>2553</v>
+        <v>2552</v>
       </c>
     </row>
     <row r="2555" spans="1:1">
       <c r="A2555" t="s">
-        <v>2554</v>
+        <v>2553</v>
       </c>
     </row>
     <row r="2556" spans="1:1">
       <c r="A2556" t="s">
-        <v>2555</v>
+        <v>2554</v>
       </c>
     </row>
     <row r="2557" spans="1:1">
       <c r="A2557" t="s">
-        <v>2556</v>
+        <v>2555</v>
       </c>
     </row>
     <row r="2558" spans="1:1">
       <c r="A2558" t="s">
-        <v>661</v>
+        <v>2556</v>
       </c>
     </row>
     <row r="2559" spans="1:1">
@@ -24893,53 +24866,8 @@
       </c>
     </row>
     <row r="2983" spans="1:1">
-      <c r="A2983" t="s">
+      <c r="A2983" s="1" t="s">
         <v>2981</v>
-      </c>
-    </row>
-    <row r="2984" spans="1:1">
-      <c r="A2984" t="s">
-        <v>2982</v>
-      </c>
-    </row>
-    <row r="2985" spans="1:1">
-      <c r="A2985" t="s">
-        <v>2983</v>
-      </c>
-    </row>
-    <row r="2986" spans="1:1">
-      <c r="A2986" t="s">
-        <v>2984</v>
-      </c>
-    </row>
-    <row r="2987" spans="1:1">
-      <c r="A2987" t="s">
-        <v>2985</v>
-      </c>
-    </row>
-    <row r="2988" spans="1:1">
-      <c r="A2988" t="s">
-        <v>2986</v>
-      </c>
-    </row>
-    <row r="2989" spans="1:1">
-      <c r="A2989" t="s">
-        <v>2987</v>
-      </c>
-    </row>
-    <row r="2990" spans="1:1">
-      <c r="A2990" t="s">
-        <v>2988</v>
-      </c>
-    </row>
-    <row r="2991" spans="1:1">
-      <c r="A2991" t="s">
-        <v>2989</v>
-      </c>
-    </row>
-    <row r="2992" spans="1:1">
-      <c r="A2992" t="s">
-        <v>2990</v>
       </c>
     </row>
   </sheetData>
